--- a/Dowling/dowling-vs-sep-091826.xlsx
+++ b/Dowling/dowling-vs-sep-091826.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1abc75c8e08b2b2b/Desktop/GitHub/Dowling-Football/Dowling/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_0E72D6CE60D9ED2D5C600E8C80003730A18C4EBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8FE5979-1783-4614-8B08-21525DBF0293}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R9a036fa1b7de448d"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="90">
   <si>
     <t>PLAY #</t>
   </si>
@@ -285,11 +294,866 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y162"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -366,7 +1230,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -395,7 +1259,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -448,7 +1312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -501,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -554,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -607,7 +1471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -660,7 +1524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -692,7 +1556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -742,7 +1606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -792,7 +1656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -845,7 +1709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -895,7 +1759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -945,7 +1809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -995,7 +1859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1048,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1101,7 +1965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1151,7 +2015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1201,7 +2065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1233,7 +2097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1265,7 +2129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1321,7 +2185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1377,7 +2241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1430,7 +2294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1483,7 +2347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1515,7 +2379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1568,7 +2432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1618,7 +2482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1671,7 +2535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1703,7 +2567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1753,7 +2617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1809,7 +2673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1865,7 +2729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1918,7 +2782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1971,7 +2835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2024,7 +2888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2080,7 +2944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2133,7 +2997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2189,7 +3053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2242,7 +3106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2292,7 +3156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2345,7 +3209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2401,7 +3265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2454,7 +3318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2504,7 +3368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2560,7 +3424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2616,7 +3480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2648,7 +3512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2677,7 +3541,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2727,7 +3591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2780,7 +3644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2830,7 +3694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2862,7 +3726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2912,7 +3776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2962,7 +3826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3015,7 +3879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3071,7 +3935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3127,7 +3991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3180,7 +4044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3233,7 +4097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3286,7 +4150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3339,7 +4203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3371,7 +4235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3400,7 +4264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3450,7 +4314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3500,7 +4364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3550,7 +4414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3600,7 +4464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3650,7 +4514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3700,7 +4564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3753,7 +4617,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3785,7 +4649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3814,7 +4678,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3867,7 +4731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3920,7 +4784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3973,7 +4837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4005,7 +4869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4055,7 +4919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4105,7 +4969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4155,7 +5019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4187,7 +5051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4240,7 +5104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4296,7 +5160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4352,7 +5216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4408,7 +5272,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4461,7 +5325,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4493,7 +5357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4522,7 +5386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4575,7 +5439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4625,7 +5489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4675,7 +5539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4725,7 +5589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4778,7 +5642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4831,7 +5695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4884,7 +5748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4934,7 +5798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4987,7 +5851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5022,7 +5886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5054,7 +5918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5110,7 +5974,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5163,7 +6027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5216,7 +6080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5269,7 +6133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5325,7 +6189,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5378,7 +6242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5434,7 +6298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5490,7 +6354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5528,7 +6392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5581,7 +6445,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5634,7 +6498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -5687,7 +6551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5740,7 +6604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -5793,7 +6657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5846,7 +6710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5878,7 +6742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5910,7 +6774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5960,7 +6824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6013,7 +6877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6066,7 +6930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6119,7 +6983,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6169,7 +7033,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6219,7 +7083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6269,7 +7133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6322,7 +7186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6372,7 +7236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -6425,7 +7289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6457,7 +7321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -6480,13 +7344,13 @@
         <v>26</v>
       </c>
       <c r="H127" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="I127" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -6539,7 +7403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6595,7 +7459,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6645,7 +7509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -6695,7 +7559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -6745,7 +7609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -6777,7 +7641,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6806,7 +7670,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -6859,7 +7723,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -6912,7 +7776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -6968,7 +7832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7021,7 +7885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7056,7 +7920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7085,7 +7949,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7141,7 +8005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7182,7 +8046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7235,7 +8099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7267,7 +8131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7320,7 +8184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7373,7 +8237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7426,7 +8290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -7482,7 +8346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7538,7 +8402,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7591,7 +8455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7644,7 +8508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7697,7 +8561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7753,7 +8617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -7806,7 +8670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7859,7 +8723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7912,7 +8776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7968,7 +8832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8003,7 +8867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8038,7 +8902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8070,7 +8934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8099,7 +8963,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8153,5 +9017,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dowling/dowling-vs-sep-091826.xlsx
+++ b/Dowling/dowling-vs-sep-091826.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1abc75c8e08b2b2b/Desktop/GitHub/Dowling-Football/Dowling/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_0E72D6CE60D9ED2D5C600E8C80003730A18C4EBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8FE5979-1783-4614-8B08-21525DBF0293}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R46772142db914dee"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0">
   <si>
     <t>PLAY #</t>
   </si>
@@ -124,18 +115,27 @@
     <t>N</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
     <t>Y OFF TRIPS</t>
   </si>
   <si>
+    <t>E-Alley</t>
+  </si>
+  <si>
     <t>UNBALANCED PRO</t>
   </si>
   <si>
     <t>UNBALANCED TWINS</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>TWINS WING</t>
   </si>
   <si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>No Good</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>Y QUAD</t>
@@ -294,866 +297,11 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="33">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="10">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:Y162"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1230,7 +378,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1259,7 +407,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1296,14 +444,17 @@
       <c r="L3">
         <v>7</v>
       </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
       <c r="R3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -1312,7 +463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1349,14 +500,17 @@
       <c r="L4">
         <v>8</v>
       </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
       <c r="R4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -1365,7 +519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1385,7 +539,7 @@
         <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
         <v>31</v>
@@ -1402,14 +556,17 @@
       <c r="L5">
         <v>6</v>
       </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
       <c r="R5" t="s">
         <v>30</v>
       </c>
       <c r="S5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -1418,7 +575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1438,7 +595,7 @@
         <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
         <v>31</v>
@@ -1455,14 +612,17 @@
       <c r="L6">
         <v>6</v>
       </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
       <c r="R6" t="s">
         <v>30</v>
       </c>
       <c r="S6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W6">
         <v>3</v>
@@ -1471,7 +631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1491,7 +651,7 @@
         <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>31</v>
@@ -1503,28 +663,31 @@
         <v>-1</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
       <c r="R7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="U7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1544,19 +707,19 @@
         <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1564,7 +727,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1588,25 +751,25 @@
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
       <c r="R9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1614,7 +777,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -1626,7 +789,7 @@
         <v>-44</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
         <v>31</v>
@@ -1638,25 +801,25 @@
         <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="R10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1664,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1676,19 +839,19 @@
         <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J11">
         <v>14</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1696,11 +859,14 @@
       <c r="N11">
         <v>3</v>
       </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
       <c r="R11" t="s">
         <v>30</v>
       </c>
       <c r="S11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U11" t="s">
         <v>30</v>
@@ -1709,7 +875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1717,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1729,7 +895,7 @@
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
         <v>31</v>
@@ -1747,10 +913,10 @@
         <v>7</v>
       </c>
       <c r="R12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U12" t="s">
         <v>30</v>
@@ -1759,7 +925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1767,7 +933,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1791,25 +957,25 @@
         <v>8</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
       <c r="R13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1817,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1847,10 +1013,10 @@
         <v>7</v>
       </c>
       <c r="R14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U14" t="s">
         <v>30</v>
@@ -1859,7 +1025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1867,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -1882,10 +1048,10 @@
         <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J15">
         <v>3</v>
@@ -1899,20 +1065,23 @@
       <c r="N15">
         <v>1</v>
       </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
       <c r="R15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1920,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -1932,19 +1101,19 @@
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -1952,20 +1121,23 @@
       <c r="N16">
         <v>11</v>
       </c>
+      <c r="O16">
+        <v>5</v>
+      </c>
       <c r="R16" t="s">
         <v>30</v>
       </c>
       <c r="S16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1973,7 +1145,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1985,7 +1157,7 @@
         <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H17" t="s">
         <v>31</v>
@@ -1997,7 +1169,7 @@
         <v>3</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -2006,7 +1178,7 @@
         <v>30</v>
       </c>
       <c r="S17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U17" t="s">
         <v>30</v>
@@ -2015,7 +1187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2023,7 +1195,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -2041,13 +1213,13 @@
         <v>31</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -2056,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="S18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U18" t="s">
         <v>30</v>
@@ -2065,7 +1237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2088,16 +1260,16 @@
         <v>26</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2129,7 +1301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2152,10 +1324,10 @@
         <v>26</v>
       </c>
       <c r="H21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J21">
         <v>11</v>
@@ -2169,14 +1341,17 @@
       <c r="N21">
         <v>10</v>
       </c>
+      <c r="O21">
+        <v>6</v>
+      </c>
       <c r="R21" t="s">
         <v>30</v>
       </c>
       <c r="S21" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W21">
         <v>3</v>
@@ -2185,7 +1360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2205,19 +1380,19 @@
         <v>-31</v>
       </c>
       <c r="G22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -2225,11 +1400,14 @@
       <c r="N22">
         <v>7</v>
       </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
       <c r="R22" t="s">
         <v>30</v>
       </c>
       <c r="S22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U22" t="s">
         <v>30</v>
@@ -2241,7 +1419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2261,7 +1439,7 @@
         <v>-31</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H23" t="s">
         <v>31</v>
@@ -2273,16 +1451,19 @@
         <v>-5</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L23">
         <v>6</v>
       </c>
+      <c r="M23" t="s">
+        <v>29</v>
+      </c>
       <c r="R23" t="s">
         <v>30</v>
       </c>
       <c r="S23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U23" t="s">
         <v>30</v>
@@ -2294,7 +1475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2317,16 +1498,16 @@
         <v>26</v>
       </c>
       <c r="H24" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J24">
         <v>-5</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L24">
         <v>7</v>
@@ -2335,7 +1516,7 @@
         <v>30</v>
       </c>
       <c r="S24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U24" t="s">
         <v>30</v>
@@ -2347,7 +1528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2370,16 +1551,16 @@
         <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I25" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="X25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2387,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2420,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S26" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U26" t="s">
         <v>30</v>
@@ -2432,7 +1613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2440,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2473,7 +1654,7 @@
         <v>30</v>
       </c>
       <c r="S27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U27" t="s">
         <v>30</v>
@@ -2482,7 +1663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2490,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -2505,10 +1686,10 @@
         <v>30</v>
       </c>
       <c r="H28" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I28" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -2522,11 +1703,14 @@
       <c r="N28">
         <v>32</v>
       </c>
+      <c r="O28">
+        <v>7</v>
+      </c>
       <c r="R28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S28" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U28" t="s">
         <v>30</v>
@@ -2535,7 +1719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2558,16 +1742,16 @@
         <v>30</v>
       </c>
       <c r="H29" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I29" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2599,13 +1783,16 @@
         <v>-1</v>
       </c>
       <c r="K30" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
+      <c r="M30" t="s">
+        <v>67</v>
+      </c>
       <c r="R30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U30" t="s">
         <v>30</v>
@@ -2617,7 +1804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2640,16 +1827,16 @@
         <v>30</v>
       </c>
       <c r="H31" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I31" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -2657,14 +1844,17 @@
       <c r="N31">
         <v>24</v>
       </c>
+      <c r="O31">
+        <v>9</v>
+      </c>
       <c r="R31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S31" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="U31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W31">
         <v>3</v>
@@ -2673,7 +1863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2696,10 +1886,10 @@
         <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I32" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J32">
         <v>29</v>
@@ -2713,14 +1903,17 @@
       <c r="N32">
         <v>11</v>
       </c>
+      <c r="O32">
+        <v>5</v>
+      </c>
       <c r="R32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S32" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="U32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W32">
         <v>3</v>
@@ -2729,7 +1922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2766,14 +1959,17 @@
       <c r="L33">
         <v>7</v>
       </c>
+      <c r="M33" t="s">
+        <v>34</v>
+      </c>
       <c r="R33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W33">
         <v>3</v>
@@ -2782,7 +1978,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2802,7 +1998,7 @@
         <v>47</v>
       </c>
       <c r="G34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H34" t="s">
         <v>31</v>
@@ -2819,14 +2015,17 @@
       <c r="L34">
         <v>6</v>
       </c>
+      <c r="M34" t="s">
+        <v>67</v>
+      </c>
       <c r="R34" t="s">
         <v>30</v>
       </c>
       <c r="S34" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W34">
         <v>3</v>
@@ -2835,7 +2034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2855,7 +2054,7 @@
         <v>43</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H35" t="s">
         <v>31</v>
@@ -2867,19 +2066,22 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
+        <v>42</v>
+      </c>
+      <c r="L35">
+        <v>6</v>
+      </c>
+      <c r="M35" t="s">
+        <v>67</v>
+      </c>
+      <c r="R35" t="s">
+        <v>30</v>
+      </c>
+      <c r="S35" t="s">
         <v>39</v>
       </c>
-      <c r="L35">
-        <v>6</v>
-      </c>
-      <c r="R35" t="s">
-        <v>30</v>
-      </c>
-      <c r="S35" t="s">
-        <v>37</v>
-      </c>
       <c r="U35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W35">
         <v>3</v>
@@ -2888,7 +2090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2908,19 +2110,19 @@
         <v>42</v>
       </c>
       <c r="G36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I36" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L36">
         <v>7</v>
@@ -2928,14 +2130,17 @@
       <c r="N36">
         <v>40</v>
       </c>
+      <c r="O36">
+        <v>8</v>
+      </c>
       <c r="R36" t="s">
         <v>30</v>
       </c>
       <c r="S36" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="U36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W36">
         <v>3</v>
@@ -2944,7 +2149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2964,7 +2169,7 @@
         <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H37" t="s">
         <v>31</v>
@@ -2976,19 +2181,22 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L37">
         <v>6</v>
       </c>
+      <c r="M37" t="s">
+        <v>34</v>
+      </c>
       <c r="R37" t="s">
         <v>30</v>
       </c>
       <c r="S37" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W37">
         <v>3</v>
@@ -2997,7 +2205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3017,13 +2225,13 @@
         <v>42</v>
       </c>
       <c r="G38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I38" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J38">
         <v>13</v>
@@ -3037,14 +2245,17 @@
       <c r="N38">
         <v>6</v>
       </c>
+      <c r="O38">
+        <v>2</v>
+      </c>
       <c r="R38" t="s">
         <v>30</v>
       </c>
       <c r="S38" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W38">
         <v>6</v>
@@ -3053,7 +2264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3073,7 +2284,7 @@
         <v>29</v>
       </c>
       <c r="G39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H39" t="s">
         <v>31</v>
@@ -3090,11 +2301,14 @@
       <c r="L39">
         <v>8</v>
       </c>
+      <c r="M39" t="s">
+        <v>29</v>
+      </c>
       <c r="R39" t="s">
         <v>30</v>
       </c>
       <c r="S39" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="U39" t="s">
         <v>30</v>
@@ -3106,7 +2320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3126,13 +2340,13 @@
         <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H40" t="s">
         <v>31</v>
       </c>
       <c r="I40" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J40">
         <v>5</v>
@@ -3147,7 +2361,7 @@
         <v>30</v>
       </c>
       <c r="S40" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="W40">
         <v>3</v>
@@ -3156,7 +2370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3176,7 +2390,7 @@
         <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H41" t="s">
         <v>31</v>
@@ -3193,11 +2407,14 @@
       <c r="L41">
         <v>7</v>
       </c>
+      <c r="M41" t="s">
+        <v>29</v>
+      </c>
       <c r="R41" t="s">
         <v>30</v>
       </c>
       <c r="S41" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U41" t="s">
         <v>30</v>
@@ -3209,7 +2426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3232,16 +2449,16 @@
         <v>26</v>
       </c>
       <c r="H42" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I42" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L42">
         <v>6</v>
@@ -3249,23 +2466,26 @@
       <c r="N42">
         <v>7</v>
       </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
       <c r="R42" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S42" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="U42" t="s">
         <v>30</v>
       </c>
       <c r="W42" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="X42">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3302,23 +2522,26 @@
       <c r="L43">
         <v>8</v>
       </c>
+      <c r="M43" t="s">
+        <v>29</v>
+      </c>
       <c r="R43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S43" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U43" t="s">
         <v>30</v>
       </c>
       <c r="W43" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X43">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3350,25 +2573,28 @@
         <v>-2</v>
       </c>
       <c r="K44" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L44">
         <v>10</v>
       </c>
+      <c r="M44" t="s">
+        <v>29</v>
+      </c>
       <c r="R44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W44" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="X44">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3391,16 +2617,16 @@
         <v>26</v>
       </c>
       <c r="H45" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I45" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L45">
         <v>7</v>
@@ -3408,11 +2634,14 @@
       <c r="N45">
         <v>11</v>
       </c>
+      <c r="O45">
+        <v>4</v>
+      </c>
       <c r="R45" t="s">
         <v>30</v>
       </c>
       <c r="S45" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U45" t="s">
         <v>30</v>
@@ -3424,7 +2653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3447,16 +2676,16 @@
         <v>26</v>
       </c>
       <c r="H46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L46">
         <v>9</v>
@@ -3464,23 +2693,26 @@
       <c r="N46">
         <v>5</v>
       </c>
+      <c r="O46">
+        <v>1</v>
+      </c>
       <c r="R46" t="s">
         <v>30</v>
       </c>
       <c r="S46" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U46" t="s">
         <v>30</v>
       </c>
       <c r="W46" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="X46">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3503,16 +2735,16 @@
         <v>26</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I47" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3535,13 +2767,13 @@
         <v>26</v>
       </c>
       <c r="H48" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3549,7 +2781,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3579,10 +2811,10 @@
         <v>7</v>
       </c>
       <c r="R49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S49" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U49" t="s">
         <v>30</v>
@@ -3591,7 +2823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3599,7 +2831,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -3614,16 +2846,16 @@
         <v>30</v>
       </c>
       <c r="H50" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I50" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J50">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L50">
         <v>5</v>
@@ -3631,20 +2863,23 @@
       <c r="N50">
         <v>6</v>
       </c>
+      <c r="O50">
+        <v>2</v>
+      </c>
       <c r="R50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S50" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="U50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X50">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3652,7 +2887,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -3682,19 +2917,19 @@
         <v>8</v>
       </c>
       <c r="R51" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S51" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="U51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3714,19 +2949,19 @@
         <v>-29</v>
       </c>
       <c r="G52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="X52">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3763,11 +2998,14 @@
       <c r="L53">
         <v>6</v>
       </c>
+      <c r="M53" t="s">
+        <v>29</v>
+      </c>
       <c r="Q53">
         <v>0</v>
       </c>
       <c r="U53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W53">
         <v>3</v>
@@ -3776,7 +3014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3808,16 +3046,19 @@
         <v>3</v>
       </c>
       <c r="K54" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L54">
         <v>7</v>
       </c>
+      <c r="M54" t="s">
+        <v>40</v>
+      </c>
       <c r="R54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S54" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U54" t="s">
         <v>30</v>
@@ -3826,7 +3067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3858,19 +3099,22 @@
         <v>3</v>
       </c>
       <c r="K55" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L55">
         <v>7</v>
       </c>
+      <c r="M55" t="s">
+        <v>29</v>
+      </c>
       <c r="R55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S55" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="U55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W55">
         <v>3</v>
@@ -3879,7 +3123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3902,16 +3146,16 @@
         <v>30</v>
       </c>
       <c r="H56" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I56" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -3919,14 +3163,17 @@
       <c r="N56">
         <v>7</v>
       </c>
+      <c r="O56">
+        <v>3</v>
+      </c>
       <c r="R56" t="s">
         <v>30</v>
       </c>
       <c r="S56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W56">
         <v>3</v>
@@ -3935,7 +3182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3958,10 +3205,10 @@
         <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I57" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J57">
         <v>9</v>
@@ -3975,11 +3222,14 @@
       <c r="N57">
         <v>6</v>
       </c>
+      <c r="O57">
+        <v>2</v>
+      </c>
       <c r="R57" t="s">
         <v>30</v>
       </c>
       <c r="S57" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U57" t="s">
         <v>30</v>
@@ -3991,7 +3241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4028,11 +3278,14 @@
       <c r="L58">
         <v>6</v>
       </c>
+      <c r="M58" t="s">
+        <v>29</v>
+      </c>
       <c r="R58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S58" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U58" t="s">
         <v>30</v>
@@ -4044,7 +3297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4081,11 +3334,14 @@
       <c r="L59">
         <v>6</v>
       </c>
+      <c r="M59" t="s">
+        <v>34</v>
+      </c>
       <c r="R59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S59" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U59" t="s">
         <v>30</v>
@@ -4097,7 +3353,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4134,23 +3390,26 @@
       <c r="L60">
         <v>8</v>
       </c>
+      <c r="M60" t="s">
+        <v>29</v>
+      </c>
       <c r="R60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S60" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W60" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="X60">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4176,7 +3435,7 @@
         <v>31</v>
       </c>
       <c r="I61" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -4187,23 +3446,26 @@
       <c r="L61">
         <v>9</v>
       </c>
+      <c r="M61" t="s">
+        <v>29</v>
+      </c>
       <c r="R61" t="s">
         <v>30</v>
       </c>
       <c r="S61" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="U61" t="s">
         <v>30</v>
       </c>
       <c r="W61" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="X61">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4226,16 +3488,16 @@
         <v>26</v>
       </c>
       <c r="H62" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I62" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X62">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4258,13 +3520,13 @@
         <v>30</v>
       </c>
       <c r="H63" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4272,7 +3534,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -4296,16 +3558,16 @@
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L64">
         <v>6</v>
       </c>
       <c r="R64" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S64" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U64" t="s">
         <v>30</v>
@@ -4314,7 +3576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4322,7 +3584,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -4346,16 +3608,16 @@
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L65">
         <v>6</v>
       </c>
       <c r="R65" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S65" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U65" t="s">
         <v>30</v>
@@ -4364,7 +3626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4372,7 +3634,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -4396,25 +3658,25 @@
         <v>3</v>
       </c>
       <c r="K66" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L66">
         <v>6</v>
       </c>
       <c r="R66" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S66" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X66">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4422,7 +3684,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -4437,25 +3699,25 @@
         <v>26</v>
       </c>
       <c r="H67" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I67" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J67">
         <v>14</v>
       </c>
       <c r="K67" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L67">
         <v>6</v>
       </c>
       <c r="R67" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S67" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U67" t="s">
         <v>30</v>
@@ -4464,7 +3726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4472,7 +3734,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -4496,16 +3758,16 @@
         <v>16</v>
       </c>
       <c r="K68" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L68">
         <v>6</v>
       </c>
       <c r="R68" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S68" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U68" t="s">
         <v>30</v>
@@ -4514,7 +3776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4522,7 +3784,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -4552,10 +3814,10 @@
         <v>6</v>
       </c>
       <c r="R69" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S69" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U69" t="s">
         <v>30</v>
@@ -4564,7 +3826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="70">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4572,7 +3834,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -4587,16 +3849,16 @@
         <v>30</v>
       </c>
       <c r="H70" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I70" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J70">
         <v>41</v>
       </c>
       <c r="K70" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L70">
         <v>6</v>
@@ -4604,11 +3866,14 @@
       <c r="N70">
         <v>39</v>
       </c>
+      <c r="O70">
+        <v>7</v>
+      </c>
       <c r="R70" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S70" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U70" t="s">
         <v>30</v>
@@ -4617,7 +3882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4640,16 +3905,16 @@
         <v>26</v>
       </c>
       <c r="H71" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I71" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X71">
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4678,7 +3943,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4715,11 +3980,14 @@
       <c r="L73">
         <v>7</v>
       </c>
+      <c r="M73" t="s">
+        <v>40</v>
+      </c>
       <c r="R73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S73" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U73" t="s">
         <v>30</v>
@@ -4731,7 +3999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4768,14 +4036,17 @@
       <c r="L74">
         <v>7</v>
       </c>
+      <c r="M74" t="s">
+        <v>34</v>
+      </c>
       <c r="R74" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S74" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="U74" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W74">
         <v>3</v>
@@ -4784,7 +4055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4816,16 +4087,19 @@
         <v>14</v>
       </c>
       <c r="K75" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L75">
         <v>7</v>
       </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
       <c r="R75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S75" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U75" t="s">
         <v>30</v>
@@ -4837,7 +4111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4860,7 +4134,7 @@
         <v>26</v>
       </c>
       <c r="H76" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s">
         <v>28</v>
@@ -4869,7 +4143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4877,7 +4151,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -4907,10 +4181,10 @@
         <v>6</v>
       </c>
       <c r="R77" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S77" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U77" t="s">
         <v>30</v>
@@ -4919,7 +4193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4927,7 +4201,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -4951,25 +4225,25 @@
         <v>5</v>
       </c>
       <c r="K78" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L78">
         <v>6</v>
       </c>
       <c r="R78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S78" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X78">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4977,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D79">
         <v>3</v>
@@ -5007,19 +4281,19 @@
         <v>6</v>
       </c>
       <c r="R79" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S79" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U79" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X79">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5039,19 +4313,19 @@
         <v>-21</v>
       </c>
       <c r="G80" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H80" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I80" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X80">
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5083,16 +4357,19 @@
         <v>-2</v>
       </c>
       <c r="K81" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L81">
         <v>7</v>
       </c>
+      <c r="M81" t="s">
+        <v>29</v>
+      </c>
       <c r="R81" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S81" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="U81" t="s">
         <v>30</v>
@@ -5104,7 +4381,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5127,16 +4404,16 @@
         <v>30</v>
       </c>
       <c r="H82" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I82" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L82">
         <v>6</v>
@@ -5144,14 +4421,17 @@
       <c r="N82">
         <v>15</v>
       </c>
+      <c r="O82">
+        <v>5</v>
+      </c>
       <c r="R82" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S82" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U82" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W82">
         <v>3</v>
@@ -5160,7 +4440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="83">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5183,10 +4463,10 @@
         <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I83" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J83">
         <v>19</v>
@@ -5200,11 +4480,14 @@
       <c r="N83">
         <v>15</v>
       </c>
+      <c r="O83">
+        <v>5</v>
+      </c>
       <c r="R83" t="s">
         <v>30</v>
       </c>
       <c r="S83" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U83" t="s">
         <v>30</v>
@@ -5216,7 +4499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="84">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5239,10 +4522,10 @@
         <v>30</v>
       </c>
       <c r="H84" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I84" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J84">
         <v>20</v>
@@ -5256,23 +4539,26 @@
       <c r="N84">
         <v>16</v>
       </c>
+      <c r="O84">
+        <v>4</v>
+      </c>
       <c r="R84" t="s">
         <v>30</v>
       </c>
       <c r="S84" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U84" t="s">
         <v>30</v>
       </c>
       <c r="W84" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X84">
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="85">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5298,7 +4584,7 @@
         <v>31</v>
       </c>
       <c r="I85" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J85">
         <v>18</v>
@@ -5309,11 +4595,14 @@
       <c r="L85">
         <v>7</v>
       </c>
+      <c r="M85" t="s">
+        <v>40</v>
+      </c>
       <c r="R85" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S85" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U85" t="s">
         <v>30</v>
@@ -5325,7 +4614,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="86">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5348,16 +4637,16 @@
         <v>26</v>
       </c>
       <c r="H86" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I86" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X86">
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="87">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5380,13 +4669,13 @@
         <v>26</v>
       </c>
       <c r="H87" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I87" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="88">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5394,7 +4683,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -5409,10 +4698,10 @@
         <v>26</v>
       </c>
       <c r="H88" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I88" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5426,20 +4715,23 @@
       <c r="N88">
         <v>45</v>
       </c>
+      <c r="O88">
+        <v>9</v>
+      </c>
       <c r="R88" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S88" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U88" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X88">
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="89">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5447,7 +4739,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -5462,25 +4754,25 @@
         <v>26</v>
       </c>
       <c r="H89" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I89" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J89">
         <v>9</v>
       </c>
       <c r="K89" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L89">
         <v>6</v>
       </c>
       <c r="R89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S89" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U89" t="s">
         <v>30</v>
@@ -5489,7 +4781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="90">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5497,7 +4789,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -5521,25 +4813,25 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L90">
         <v>8</v>
       </c>
       <c r="R90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S90" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X90">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="91">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5547,7 +4839,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -5571,16 +4863,16 @@
         <v>5</v>
       </c>
       <c r="K91" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L91">
         <v>6</v>
       </c>
       <c r="R91" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S91" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U91" t="s">
         <v>30</v>
@@ -5589,7 +4881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="92">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5597,7 +4889,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -5612,16 +4904,16 @@
         <v>30</v>
       </c>
       <c r="H92" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I92" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J92">
         <v>7</v>
       </c>
       <c r="K92" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L92">
         <v>6</v>
@@ -5629,11 +4921,14 @@
       <c r="N92">
         <v>6</v>
       </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
       <c r="R92" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S92" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U92" t="s">
         <v>30</v>
@@ -5642,7 +4937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="93">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5650,7 +4945,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -5665,16 +4960,16 @@
         <v>30</v>
       </c>
       <c r="H93" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I93" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J93">
         <v>18</v>
       </c>
       <c r="K93" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L93">
         <v>5</v>
@@ -5682,20 +4977,23 @@
       <c r="N93">
         <v>0</v>
       </c>
+      <c r="O93">
+        <v>2</v>
+      </c>
       <c r="R93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S93" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X93">
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="94">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5703,7 +5001,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -5715,13 +5013,13 @@
         <v>39</v>
       </c>
       <c r="G94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H94" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I94" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5735,11 +5033,14 @@
       <c r="N94">
         <v>45</v>
       </c>
+      <c r="O94">
+        <v>7</v>
+      </c>
       <c r="R94" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S94" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U94" t="s">
         <v>30</v>
@@ -5748,7 +5049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="95">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5756,7 +5057,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D95">
         <v>2</v>
@@ -5768,7 +5069,7 @@
         <v>39</v>
       </c>
       <c r="G95" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H95" t="s">
         <v>31</v>
@@ -5786,10 +5087,10 @@
         <v>5</v>
       </c>
       <c r="R95" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S95" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U95" t="s">
         <v>30</v>
@@ -5798,7 +5099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="96">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5806,7 +5107,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -5821,10 +5122,10 @@
         <v>30</v>
       </c>
       <c r="H96" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I96" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5838,20 +5139,23 @@
       <c r="N96">
         <v>10</v>
       </c>
+      <c r="O96">
+        <v>6</v>
+      </c>
       <c r="R96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S96" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X96">
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="97">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5874,10 +5178,10 @@
         <v>30</v>
       </c>
       <c r="H97" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I97" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J97">
         <v>-5</v>
@@ -5886,7 +5190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="98">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5909,16 +5213,16 @@
         <v>30</v>
       </c>
       <c r="H98" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I98" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="X98">
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="99">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5938,7 +5242,7 @@
         <v>-10</v>
       </c>
       <c r="G99" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H99" t="s">
         <v>31</v>
@@ -5950,10 +5254,13 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L99">
         <v>6</v>
+      </c>
+      <c r="M99" t="s">
+        <v>29</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -5962,7 +5269,7 @@
         <v>30</v>
       </c>
       <c r="S99" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U99" t="s">
         <v>30</v>
@@ -5974,7 +5281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="100">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6011,23 +5318,26 @@
       <c r="L100">
         <v>6</v>
       </c>
+      <c r="M100" t="s">
+        <v>67</v>
+      </c>
       <c r="R100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S100" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W100" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X100">
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="101">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6047,7 +5357,7 @@
         <v>-29</v>
       </c>
       <c r="G101" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H101" t="s">
         <v>31</v>
@@ -6064,14 +5374,17 @@
       <c r="L101">
         <v>6</v>
       </c>
+      <c r="M101" t="s">
+        <v>40</v>
+      </c>
       <c r="R101" t="s">
         <v>30</v>
       </c>
       <c r="S101" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U101" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W101">
         <v>3</v>
@@ -6080,7 +5393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="102">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6100,7 +5413,7 @@
         <v>-40</v>
       </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H102" t="s">
         <v>31</v>
@@ -6112,28 +5425,31 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L102">
         <v>7</v>
       </c>
+      <c r="M102" t="s">
+        <v>40</v>
+      </c>
       <c r="R102" t="s">
         <v>30</v>
       </c>
       <c r="S102" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="U102" t="s">
         <v>30</v>
       </c>
       <c r="W102" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X102">
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="103">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6156,10 +5472,10 @@
         <v>26</v>
       </c>
       <c r="H103" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I103" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J103">
         <v>12</v>
@@ -6173,11 +5489,14 @@
       <c r="N103">
         <v>2</v>
       </c>
+      <c r="O103">
+        <v>1</v>
+      </c>
       <c r="R103" t="s">
         <v>30</v>
       </c>
       <c r="S103" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="U103" t="s">
         <v>30</v>
@@ -6189,7 +5508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="104">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6221,19 +5540,22 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L104">
         <v>6</v>
       </c>
+      <c r="M104" t="s">
+        <v>40</v>
+      </c>
       <c r="R104" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S104" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U104" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W104">
         <v>3</v>
@@ -6242,7 +5564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="105">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6265,16 +5587,16 @@
         <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I105" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J105">
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L105">
         <v>6</v>
@@ -6282,11 +5604,14 @@
       <c r="N105">
         <v>0</v>
       </c>
+      <c r="O105">
+        <v>1</v>
+      </c>
       <c r="R105" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S105" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="U105" t="s">
         <v>30</v>
@@ -6298,7 +5623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="106">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6321,16 +5646,16 @@
         <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I106" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L106">
         <v>6</v>
@@ -6338,23 +5663,26 @@
       <c r="N106">
         <v>25</v>
       </c>
+      <c r="O106">
+        <v>9</v>
+      </c>
       <c r="R106" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S106" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="U106" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W106" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X106">
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="107">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6377,7 +5705,7 @@
         <v>30</v>
       </c>
       <c r="H107" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I107" t="s">
         <v>32</v>
@@ -6386,13 +5714,13 @@
         <v>14</v>
       </c>
       <c r="U107" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X107">
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="108">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6412,7 +5740,7 @@
         <v>32</v>
       </c>
       <c r="G108" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H108" t="s">
         <v>31</v>
@@ -6424,19 +5752,22 @@
         <v>-1</v>
       </c>
       <c r="K108" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L108">
         <v>8</v>
       </c>
+      <c r="M108" t="s">
+        <v>67</v>
+      </c>
       <c r="R108" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S108" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="U108" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W108">
         <v>3</v>
@@ -6445,7 +5776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="109">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6465,13 +5796,13 @@
         <v>33</v>
       </c>
       <c r="G109" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H109" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I109" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J109">
         <v>15</v>
@@ -6485,6 +5816,9 @@
       <c r="N109">
         <v>6</v>
       </c>
+      <c r="O109">
+        <v>2</v>
+      </c>
       <c r="R109" t="s">
         <v>30</v>
       </c>
@@ -6492,13 +5826,13 @@
         <v>30</v>
       </c>
       <c r="W109" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X109">
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="110">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6518,7 +5852,7 @@
         <v>18</v>
       </c>
       <c r="G110" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H110" t="s">
         <v>31</v>
@@ -6530,28 +5864,31 @@
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L110">
         <v>8</v>
       </c>
+      <c r="M110" t="s">
+        <v>40</v>
+      </c>
       <c r="R110" t="s">
         <v>30</v>
       </c>
       <c r="S110" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="U110" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W110" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X110">
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="111">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6583,28 +5920,31 @@
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L111">
         <v>7</v>
       </c>
+      <c r="M111" t="s">
+        <v>40</v>
+      </c>
       <c r="R111" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S111" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U111" t="s">
         <v>30</v>
       </c>
       <c r="W111" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X111">
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="112">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6636,28 +5976,31 @@
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L112">
         <v>7</v>
       </c>
+      <c r="M112" t="s">
+        <v>40</v>
+      </c>
       <c r="R112" t="s">
         <v>30</v>
       </c>
       <c r="S112" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U112" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W112" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X112">
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="113">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6677,7 +6020,7 @@
         <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H113" t="s">
         <v>31</v>
@@ -6689,28 +6032,31 @@
         <v>4</v>
       </c>
       <c r="K113" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L113">
         <v>6</v>
       </c>
+      <c r="M113" t="s">
+        <v>67</v>
+      </c>
       <c r="R113" t="s">
         <v>30</v>
       </c>
       <c r="S113" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U113" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W113" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X113">
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="114">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6730,19 +6076,19 @@
         <v>11</v>
       </c>
       <c r="G114" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H114" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I114" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X114">
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="115">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6765,16 +6111,16 @@
         <v>26</v>
       </c>
       <c r="H115" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I115" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="Q115">
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="116">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6782,7 +6128,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -6806,16 +6152,16 @@
         <v>7</v>
       </c>
       <c r="K116" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L116">
         <v>6</v>
       </c>
       <c r="R116" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S116" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U116" t="s">
         <v>30</v>
@@ -6824,7 +6170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="117">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6832,7 +6178,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -6847,10 +6193,10 @@
         <v>30</v>
       </c>
       <c r="H117" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I117" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6864,20 +6210,23 @@
       <c r="N117">
         <v>9</v>
       </c>
+      <c r="O117">
+        <v>2</v>
+      </c>
       <c r="R117" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S117" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U117" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X117">
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="118">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6885,7 +6234,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D118">
         <v>3</v>
@@ -6900,16 +6249,16 @@
         <v>30</v>
       </c>
       <c r="H118" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I118" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J118">
         <v>17</v>
       </c>
       <c r="K118" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L118">
         <v>6</v>
@@ -6917,20 +6266,23 @@
       <c r="N118">
         <v>8</v>
       </c>
+      <c r="O118">
+        <v>2</v>
+      </c>
       <c r="R118" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S118" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U118" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X118">
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="119">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6938,7 +6290,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -6950,13 +6302,13 @@
         <v>-44</v>
       </c>
       <c r="G119" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H119" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I119" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6970,20 +6322,23 @@
       <c r="N119">
         <v>7</v>
       </c>
+      <c r="O119">
+        <v>3</v>
+      </c>
       <c r="R119" t="s">
         <v>30</v>
       </c>
       <c r="S119" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U119" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X119">
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="120">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6991,7 +6346,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -7003,7 +6358,7 @@
         <v>-44</v>
       </c>
       <c r="G120" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H120" t="s">
         <v>31</v>
@@ -7015,25 +6370,25 @@
         <v>16</v>
       </c>
       <c r="K120" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L120">
         <v>5</v>
       </c>
       <c r="R120" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S120" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U120" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X120">
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="121">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7041,7 +6396,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -7053,7 +6408,7 @@
         <v>40</v>
       </c>
       <c r="G121" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H121" t="s">
         <v>31</v>
@@ -7074,7 +6429,7 @@
         <v>30</v>
       </c>
       <c r="S121" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U121" t="s">
         <v>30</v>
@@ -7083,7 +6438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="122">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7091,7 +6446,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -7121,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="R122" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S122" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U122" t="s">
         <v>30</v>
@@ -7133,7 +6488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="123">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7141,7 +6496,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -7156,16 +6511,16 @@
         <v>26</v>
       </c>
       <c r="H123" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I123" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J123">
         <v>15</v>
       </c>
       <c r="K123" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L123">
         <v>5</v>
@@ -7173,11 +6528,14 @@
       <c r="N123">
         <v>40</v>
       </c>
+      <c r="O123">
+        <v>7</v>
+      </c>
       <c r="R123" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S123" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U123" t="s">
         <v>30</v>
@@ -7186,7 +6544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="124">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7194,7 +6552,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -7218,25 +6576,25 @@
         <v>8</v>
       </c>
       <c r="K124" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L124">
         <v>7</v>
       </c>
       <c r="R124" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S124" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U124" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X124">
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="125">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7244,7 +6602,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -7256,19 +6614,19 @@
         <v>12</v>
       </c>
       <c r="G125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H125" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I125" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J125">
         <v>12</v>
       </c>
       <c r="K125" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L125">
         <v>7</v>
@@ -7276,11 +6634,14 @@
       <c r="N125">
         <v>13</v>
       </c>
+      <c r="O125">
+        <v>5</v>
+      </c>
       <c r="R125" t="s">
         <v>30</v>
       </c>
       <c r="S125" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U125" t="s">
         <v>30</v>
@@ -7289,7 +6650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="126">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7312,16 +6673,16 @@
         <v>26</v>
       </c>
       <c r="H126" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I126" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X126">
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="127">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7350,7 +6711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="128">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7382,16 +6743,19 @@
         <v>3</v>
       </c>
       <c r="K128" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L128">
         <v>7</v>
       </c>
+      <c r="M128" t="s">
+        <v>67</v>
+      </c>
       <c r="R128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S128" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U128" t="s">
         <v>30</v>
@@ -7403,7 +6767,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="129">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7426,16 +6790,16 @@
         <v>30</v>
       </c>
       <c r="H129" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I129" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J129">
         <v>3</v>
       </c>
       <c r="K129" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L129">
         <v>7</v>
@@ -7443,14 +6807,17 @@
       <c r="N129">
         <v>3</v>
       </c>
+      <c r="O129">
+        <v>3</v>
+      </c>
       <c r="R129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S129" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W129">
         <v>3</v>
@@ -7459,7 +6826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="130">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7467,7 +6834,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -7485,31 +6852,31 @@
         <v>31</v>
       </c>
       <c r="I130" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J130">
         <v>17</v>
       </c>
       <c r="K130" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L130">
         <v>6</v>
       </c>
       <c r="R130" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S130" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U130" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X130">
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="131">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7517,7 +6884,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -7529,7 +6896,7 @@
         <v>14</v>
       </c>
       <c r="G131" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H131" t="s">
         <v>31</v>
@@ -7541,25 +6908,25 @@
         <v>10</v>
       </c>
       <c r="K131" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L131">
         <v>6</v>
       </c>
       <c r="R131" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S131" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U131" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X131">
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="132">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7567,7 +6934,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -7579,37 +6946,37 @@
         <v>4</v>
       </c>
       <c r="G132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H132" t="s">
         <v>31</v>
       </c>
       <c r="I132" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J132">
         <v>4</v>
       </c>
       <c r="K132" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L132">
         <v>7</v>
       </c>
       <c r="R132" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S132" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X132">
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="133">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7632,16 +6999,16 @@
         <v>26</v>
       </c>
       <c r="H133" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I133" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X133">
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="134">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7670,7 +7037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="135">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7707,23 +7074,26 @@
       <c r="L135">
         <v>7</v>
       </c>
+      <c r="M135" t="s">
+        <v>29</v>
+      </c>
       <c r="R135" t="s">
         <v>30</v>
       </c>
       <c r="S135" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U135" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W135" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X135">
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="136">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7743,7 +7113,7 @@
         <v>-29</v>
       </c>
       <c r="G136" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H136" t="s">
         <v>31</v>
@@ -7760,23 +7130,26 @@
       <c r="L136">
         <v>7</v>
       </c>
+      <c r="M136" t="s">
+        <v>29</v>
+      </c>
       <c r="R136" t="s">
         <v>30</v>
       </c>
       <c r="S136" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U136" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W136" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X136">
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="137">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7796,13 +7169,13 @@
         <v>-33</v>
       </c>
       <c r="G137" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H137" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I137" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J137">
         <v>15</v>
@@ -7816,23 +7189,26 @@
       <c r="N137">
         <v>28</v>
       </c>
+      <c r="O137">
+        <v>8</v>
+      </c>
       <c r="R137" t="s">
         <v>30</v>
       </c>
       <c r="S137" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U137" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W137" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X137">
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="138">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7852,13 +7228,13 @@
         <v>-48</v>
       </c>
       <c r="G138" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H138" t="s">
         <v>31</v>
       </c>
       <c r="I138" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J138">
         <v>52</v>
@@ -7869,23 +7245,26 @@
       <c r="L138">
         <v>7</v>
       </c>
+      <c r="M138" t="s">
+        <v>40</v>
+      </c>
       <c r="R138" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S138" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U138" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W138" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X138">
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="139">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7908,19 +7287,19 @@
         <v>26</v>
       </c>
       <c r="H139" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I139" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="U139" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X139">
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="140">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7943,13 +7322,13 @@
         <v>26</v>
       </c>
       <c r="H140" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I140" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="141">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7957,7 +7336,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -7972,10 +7351,10 @@
         <v>30</v>
       </c>
       <c r="H141" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I141" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J141">
         <v>0</v>
@@ -7989,23 +7368,26 @@
       <c r="N141">
         <v>43</v>
       </c>
+      <c r="O141">
+        <v>9</v>
+      </c>
       <c r="Q141">
         <v>0</v>
       </c>
       <c r="R141" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S141" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U141" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X141">
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="142">
       <c r="A142">
         <v>141</v>
       </c>
@@ -8013,7 +7395,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D142">
         <v>2</v>
@@ -8046,7 +7428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="143">
       <c r="A143">
         <v>142</v>
       </c>
@@ -8054,7 +7436,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D143">
         <v>3</v>
@@ -8069,10 +7451,10 @@
         <v>30</v>
       </c>
       <c r="H143" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I143" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -8086,11 +7468,14 @@
       <c r="N143">
         <v>10</v>
       </c>
+      <c r="O143">
+        <v>4</v>
+      </c>
       <c r="R143" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S143" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U143" t="s">
         <v>30</v>
@@ -8099,7 +7484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="144">
       <c r="A144">
         <v>143</v>
       </c>
@@ -8122,16 +7507,16 @@
         <v>30</v>
       </c>
       <c r="H144" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I144" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X144">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="145">
       <c r="A145">
         <v>144</v>
       </c>
@@ -8151,7 +7536,7 @@
         <v>-17</v>
       </c>
       <c r="G145" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H145" t="s">
         <v>31</v>
@@ -8163,28 +7548,31 @@
         <v>1</v>
       </c>
       <c r="K145" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L145">
         <v>7</v>
       </c>
+      <c r="M145" t="s">
+        <v>29</v>
+      </c>
       <c r="R145" t="s">
         <v>30</v>
       </c>
       <c r="S145" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U145" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W145" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X145">
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="146">
       <c r="A146">
         <v>145</v>
       </c>
@@ -8204,13 +7592,13 @@
         <v>-18</v>
       </c>
       <c r="G146" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H146" t="s">
         <v>31</v>
       </c>
       <c r="I146" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J146">
         <v>15</v>
@@ -8221,23 +7609,26 @@
       <c r="L146">
         <v>8</v>
       </c>
+      <c r="M146" t="s">
+        <v>67</v>
+      </c>
       <c r="R146" t="s">
         <v>30</v>
       </c>
       <c r="S146" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U146" t="s">
         <v>30</v>
       </c>
       <c r="W146" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X146">
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="147">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8257,7 +7648,7 @@
         <v>-33</v>
       </c>
       <c r="G147" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H147" t="s">
         <v>31</v>
@@ -8269,28 +7660,31 @@
         <v>-2</v>
       </c>
       <c r="K147" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L147">
         <v>8</v>
       </c>
+      <c r="M147" t="s">
+        <v>67</v>
+      </c>
       <c r="R147" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S147" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U147" t="s">
         <v>30</v>
       </c>
       <c r="W147" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X147">
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="148">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8313,16 +7707,16 @@
         <v>26</v>
       </c>
       <c r="H148" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I148" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L148">
         <v>7</v>
@@ -8330,23 +7724,26 @@
       <c r="N148">
         <v>14</v>
       </c>
+      <c r="O148">
+        <v>5</v>
+      </c>
       <c r="R148" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S148" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U148" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W148" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X148">
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="149">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8369,10 +7766,10 @@
         <v>26</v>
       </c>
       <c r="H149" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I149" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J149">
         <v>13</v>
@@ -8386,23 +7783,26 @@
       <c r="N149">
         <v>12</v>
       </c>
+      <c r="O149">
+        <v>5</v>
+      </c>
       <c r="R149" t="s">
         <v>30</v>
       </c>
       <c r="S149" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U149" t="s">
         <v>30</v>
       </c>
       <c r="W149" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X149">
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="150">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8439,23 +7839,26 @@
       <c r="L150">
         <v>8</v>
       </c>
+      <c r="M150" t="s">
+        <v>29</v>
+      </c>
       <c r="R150" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S150" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="U150" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W150" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X150">
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="151">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8475,7 +7878,7 @@
         <v>49</v>
       </c>
       <c r="G151" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H151" t="s">
         <v>31</v>
@@ -8492,23 +7895,26 @@
       <c r="L151">
         <v>7</v>
       </c>
+      <c r="M151" t="s">
+        <v>29</v>
+      </c>
       <c r="R151" t="s">
         <v>30</v>
       </c>
       <c r="S151" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U151" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W151" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X151">
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="152">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8528,7 +7934,7 @@
         <v>43</v>
       </c>
       <c r="G152" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H152" t="s">
         <v>31</v>
@@ -8545,23 +7951,26 @@
       <c r="L152">
         <v>7</v>
       </c>
+      <c r="M152" t="s">
+        <v>67</v>
+      </c>
       <c r="R152" t="s">
         <v>30</v>
       </c>
       <c r="S152" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U152" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W152" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X152">
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="153">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8581,19 +7990,19 @@
         <v>39</v>
       </c>
       <c r="G153" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H153" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I153" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L153">
         <v>7</v>
@@ -8601,23 +8010,26 @@
       <c r="N153">
         <v>14</v>
       </c>
+      <c r="O153">
+        <v>6</v>
+      </c>
       <c r="R153" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S153" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U153" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W153" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X153">
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="154">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8637,7 +8049,7 @@
         <v>39</v>
       </c>
       <c r="G154" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H154" t="s">
         <v>31</v>
@@ -8654,23 +8066,26 @@
       <c r="L154">
         <v>8</v>
       </c>
+      <c r="M154" t="s">
+        <v>29</v>
+      </c>
       <c r="R154" t="s">
         <v>30</v>
       </c>
       <c r="S154" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="U154" t="s">
         <v>30</v>
       </c>
       <c r="W154" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X154">
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="155">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8693,37 +8108,37 @@
         <v>30</v>
       </c>
       <c r="H155" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I155" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J155">
         <v>-5</v>
       </c>
       <c r="K155" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L155">
         <v>6</v>
       </c>
       <c r="R155" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S155" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="U155" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W155" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="X155">
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="156">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8755,28 +8170,31 @@
         <v>-1</v>
       </c>
       <c r="K156" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L156">
         <v>9</v>
       </c>
+      <c r="M156" t="s">
+        <v>29</v>
+      </c>
       <c r="R156" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S156" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="U156" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W156" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X156">
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="157">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8796,19 +8214,19 @@
         <v>33</v>
       </c>
       <c r="G157" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H157" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I157" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J157">
         <v>15</v>
       </c>
       <c r="K157" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L157">
         <v>6</v>
@@ -8816,23 +8234,26 @@
       <c r="N157">
         <v>14</v>
       </c>
+      <c r="O157">
+        <v>6</v>
+      </c>
       <c r="R157" t="s">
         <v>30</v>
       </c>
       <c r="S157" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U157" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W157" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="X157">
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="158">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8852,13 +8273,13 @@
         <v>18</v>
       </c>
       <c r="G158" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H158" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I158" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -8867,7 +8288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="159">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8887,13 +8308,13 @@
         <v>18</v>
       </c>
       <c r="G159" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H159" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I159" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -8902,7 +8323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="160">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8922,19 +8343,19 @@
         <v>18</v>
       </c>
       <c r="G160" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H160" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I160" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="X160">
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="161">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8957,13 +8378,13 @@
         <v>30</v>
       </c>
       <c r="H161" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I161" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="162" spans="1:24" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="162">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8971,7 +8392,7 @@
         <v>4</v>
       </c>
       <c r="C162" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -8986,10 +8407,10 @@
         <v>30</v>
       </c>
       <c r="H162" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I162" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J162">
         <v>0</v>
@@ -9000,14 +8421,17 @@
       <c r="N162">
         <v>18</v>
       </c>
+      <c r="O162">
+        <v>5</v>
+      </c>
       <c r="Q162">
         <v>0</v>
       </c>
       <c r="R162" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S162" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U162" t="s">
         <v>30</v>
@@ -9017,6 +8441,5 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dowling/dowling-vs-sep-091826.xlsx
+++ b/Dowling/dowling-vs-sep-091826.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R46772142db914dee"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R0147a9f42dd64263"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -118,6 +130,12 @@
     <t>C</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>TANK</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -127,27 +145,42 @@
     <t>E-Alley</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
+    <t>TANGO</t>
+  </si>
+  <si>
     <t>UNBALANCED PRO</t>
   </si>
   <si>
+    <t>MIAMI</t>
+  </si>
+  <si>
     <t>UNBALANCED TWINS</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>RINGO</t>
+  </si>
+  <si>
     <t>TWINS WING</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
+    <t>IOWA</t>
+  </si>
+  <si>
+    <t>FIRE OUT</t>
+  </si>
+  <si>
     <t>PRO WING</t>
   </si>
   <si>
-    <t>IOWA</t>
-  </si>
-  <si>
     <t>Punt Rec</t>
   </si>
   <si>
@@ -169,12 +202,18 @@
     <t>Complete</t>
   </si>
   <si>
+    <t>G TUCK</t>
+  </si>
+  <si>
     <t>TWINS OPEN</t>
   </si>
   <si>
     <t>TWINS PRO</t>
   </si>
   <si>
+    <t>G GUN</t>
+  </si>
+  <si>
     <t>TRIPS PRO</t>
   </si>
   <si>
@@ -196,6 +235,9 @@
     <t>Incomplete</t>
   </si>
   <si>
+    <t>STR TEX</t>
+  </si>
+  <si>
     <t>TRIPS</t>
   </si>
   <si>
@@ -205,6 +247,9 @@
     <t>Sack</t>
   </si>
   <si>
+    <t>FLEX</t>
+  </si>
+  <si>
     <t>Out of Bounds</t>
   </si>
   <si>
@@ -217,25 +262,61 @@
     <t>A</t>
   </si>
   <si>
+    <t>STEM OL MISS</t>
+  </si>
+  <si>
     <t>Y QUAD</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>EMPTY</t>
   </si>
   <si>
+    <t>K GUN</t>
+  </si>
+  <si>
+    <t>FLEX TANGO</t>
+  </si>
+  <si>
     <t>Y TRIPS OVER</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
+    <t>OLE MISS</t>
+  </si>
+  <si>
     <t>WING TRIPS</t>
   </si>
   <si>
+    <t>ARMY</t>
+  </si>
+  <si>
+    <t>FLEX TEX</t>
+  </si>
+  <si>
+    <t>KNIFE</t>
+  </si>
+  <si>
     <t>Penalty</t>
   </si>
   <si>
+    <t>GUN STACK G</t>
+  </si>
+  <si>
+    <t>OMAHA</t>
+  </si>
+  <si>
+    <t>DBL BULLET</t>
+  </si>
+  <si>
     <t>ACE</t>
   </si>
   <si>
-    <t>OMAHA</t>
+    <t>LUCKY</t>
   </si>
   <si>
     <t>Y OFF TRIPS PRO</t>
@@ -277,19 +358,43 @@
     <t>Y TRIPS CLOSED</t>
   </si>
   <si>
+    <t>G TUCK DOT</t>
+  </si>
+  <si>
     <t>UNBALANCED WING</t>
   </si>
   <si>
+    <t>WAR</t>
+  </si>
+  <si>
+    <t>WRAP</t>
+  </si>
+  <si>
     <t>Y TRIPS</t>
   </si>
   <si>
     <t>Fake Punt</t>
   </si>
   <si>
+    <t>GUN</t>
+  </si>
+  <si>
+    <t>SHADE</t>
+  </si>
+  <si>
+    <t>K TUCK</t>
+  </si>
+  <si>
+    <t>MORE</t>
+  </si>
+  <si>
     <t>Complete, Fumble</t>
   </si>
   <si>
     <t>2 Pt. Defend</t>
+  </si>
+  <si>
+    <t>G TUCK K</t>
   </si>
   <si>
     <t>Timeout</t>
@@ -299,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y162"/>
+  <dimension ref="A1:AC162"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -377,6 +482,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -386,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -398,13 +515,13 @@
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -415,7 +532,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -427,39 +544,45 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3">
         <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3">
-        <v>3</v>
-      </c>
-      <c r="X3">
+        <v>38</v>
+      </c>
+      <c r="P3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="W3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -471,7 +594,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -483,39 +606,45 @@
         <v>-28</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>22</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L4">
         <v>8</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U4" t="s">
-        <v>35</v>
-      </c>
-      <c r="W4">
-        <v>3</v>
-      </c>
-      <c r="X4">
+        <v>43</v>
+      </c>
+      <c r="P4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="W4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -527,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -539,39 +668,45 @@
         <v>50</v>
       </c>
       <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5" t="s">
-        <v>30</v>
-      </c>
-      <c r="S5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" t="s">
         <v>39</v>
       </c>
-      <c r="U5" t="s">
-        <v>35</v>
-      </c>
-      <c r="W5">
-        <v>3</v>
-      </c>
-      <c r="X5">
+      <c r="Q5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="W5" t="s">
+        <v>34</v>
+      </c>
+      <c r="X5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -583,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -595,39 +730,45 @@
         <v>46</v>
       </c>
       <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L6">
         <v>6</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
-      </c>
-      <c r="R6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S6" t="s">
-        <v>41</v>
-      </c>
-      <c r="U6" t="s">
-        <v>35</v>
-      </c>
-      <c r="W6">
-        <v>3</v>
-      </c>
-      <c r="X6">
+        <v>49</v>
+      </c>
+      <c r="P6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W6" t="s">
+        <v>34</v>
+      </c>
+      <c r="X6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -639,7 +780,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -651,39 +792,48 @@
         <v>42</v>
       </c>
       <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
         <v>35</v>
       </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
       <c r="M7" t="s">
-        <v>29</v>
-      </c>
-      <c r="R7" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="P7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>47</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
-      </c>
-      <c r="U7" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="T7" t="s">
+        <v>54</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7">
+        <v>41</v>
+      </c>
+      <c r="X7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -695,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -707,15 +857,15 @@
         <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="X8">
+        <v>57</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -727,7 +877,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -739,33 +889,36 @@
         <v>-40</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
-      <c r="R9" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" t="s">
-        <v>49</v>
-      </c>
-      <c r="U9" t="s">
-        <v>35</v>
-      </c>
-      <c r="X9">
+      <c r="P9" t="s">
+        <v>44</v>
+      </c>
+      <c r="W9" t="s">
+        <v>59</v>
+      </c>
+      <c r="X9" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -777,7 +930,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -789,33 +942,36 @@
         <v>-44</v>
       </c>
       <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
         <v>35</v>
       </c>
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J10">
         <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
-      <c r="R10" t="s">
-        <v>48</v>
-      </c>
-      <c r="S10" t="s">
-        <v>49</v>
-      </c>
-      <c r="U10" t="s">
-        <v>35</v>
-      </c>
-      <c r="X10">
+      <c r="P10" t="s">
+        <v>44</v>
+      </c>
+      <c r="W10" t="s">
+        <v>59</v>
+      </c>
+      <c r="X10" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -827,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -839,39 +995,42 @@
         <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J11">
         <v>14</v>
       </c>
       <c r="K11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11">
+        <v>6</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>44</v>
+      </c>
+      <c r="W11" t="s">
+        <v>34</v>
+      </c>
+      <c r="X11" t="s">
         <v>42</v>
       </c>
-      <c r="L11">
-        <v>6</v>
-      </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="R11" t="s">
-        <v>30</v>
-      </c>
-      <c r="S11" t="s">
-        <v>36</v>
-      </c>
-      <c r="U11" t="s">
-        <v>30</v>
-      </c>
-      <c r="X11">
+      <c r="Z11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -883,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -895,33 +1054,36 @@
         <v>30</v>
       </c>
       <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
         <v>35</v>
       </c>
-      <c r="H12" t="s">
-        <v>31</v>
-      </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J12">
         <v>3</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L12">
         <v>7</v>
       </c>
-      <c r="R12" t="s">
-        <v>35</v>
-      </c>
-      <c r="S12" t="s">
-        <v>52</v>
-      </c>
-      <c r="U12" t="s">
-        <v>30</v>
-      </c>
-      <c r="X12">
+      <c r="P12" t="s">
+        <v>63</v>
+      </c>
+      <c r="W12" t="s">
+        <v>41</v>
+      </c>
+      <c r="X12" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -933,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -945,33 +1107,36 @@
         <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J13">
         <v>8</v>
       </c>
       <c r="K13" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
-      <c r="R13" t="s">
-        <v>48</v>
-      </c>
-      <c r="S13" t="s">
-        <v>49</v>
-      </c>
-      <c r="U13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X13">
+      <c r="P13" t="s">
+        <v>44</v>
+      </c>
+      <c r="W13" t="s">
+        <v>59</v>
+      </c>
+      <c r="X13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -983,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -995,33 +1160,36 @@
         <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L14">
         <v>7</v>
       </c>
-      <c r="R14" t="s">
-        <v>35</v>
-      </c>
-      <c r="S14" t="s">
-        <v>52</v>
-      </c>
-      <c r="U14" t="s">
-        <v>30</v>
-      </c>
-      <c r="X14">
+      <c r="P14" t="s">
+        <v>63</v>
+      </c>
+      <c r="W14" t="s">
+        <v>41</v>
+      </c>
+      <c r="X14" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -1033,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -1045,19 +1213,19 @@
         <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J15">
         <v>3</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1068,16 +1236,16 @@
       <c r="O15">
         <v>3</v>
       </c>
-      <c r="R15" t="s">
-        <v>35</v>
-      </c>
-      <c r="S15" t="s">
-        <v>53</v>
-      </c>
-      <c r="U15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X15">
+      <c r="W15" t="s">
+        <v>41</v>
+      </c>
+      <c r="X15" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -1089,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -1101,19 +1269,19 @@
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
       <c r="K16" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -1124,16 +1292,19 @@
       <c r="O16">
         <v>5</v>
       </c>
-      <c r="R16" t="s">
-        <v>30</v>
-      </c>
-      <c r="S16" t="s">
-        <v>54</v>
-      </c>
-      <c r="U16" t="s">
-        <v>35</v>
-      </c>
-      <c r="X16">
+      <c r="P16" t="s">
+        <v>66</v>
+      </c>
+      <c r="W16" t="s">
+        <v>34</v>
+      </c>
+      <c r="X16" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -1145,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1157,33 +1328,36 @@
         <v>4</v>
       </c>
       <c r="G17" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" t="s">
         <v>35</v>
       </c>
-      <c r="H17" t="s">
-        <v>31</v>
-      </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J17">
         <v>3</v>
       </c>
       <c r="K17" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L17">
         <v>8</v>
       </c>
-      <c r="R17" t="s">
-        <v>30</v>
-      </c>
-      <c r="S17" t="s">
-        <v>55</v>
-      </c>
-      <c r="U17" t="s">
-        <v>30</v>
-      </c>
-      <c r="X17">
+      <c r="P17" t="s">
+        <v>66</v>
+      </c>
+      <c r="W17" t="s">
+        <v>34</v>
+      </c>
+      <c r="X17" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -1195,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1207,33 +1381,36 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L18">
         <v>7</v>
       </c>
-      <c r="R18" t="s">
-        <v>30</v>
-      </c>
-      <c r="S18" t="s">
-        <v>57</v>
-      </c>
-      <c r="U18" t="s">
-        <v>30</v>
-      </c>
-      <c r="X18">
+      <c r="P18" t="s">
+        <v>44</v>
+      </c>
+      <c r="W18" t="s">
+        <v>34</v>
+      </c>
+      <c r="X18" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -1245,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1257,15 +1434,15 @@
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I19" t="s">
-        <v>59</v>
-      </c>
-      <c r="X19">
+        <v>72</v>
+      </c>
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -1277,7 +1454,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1289,15 +1466,15 @@
         <v>-40</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I20" t="s">
-        <v>28</v>
-      </c>
-      <c r="X20">
+        <v>32</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1309,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1321,19 +1498,19 @@
         <v>-20</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J21">
         <v>11</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -1344,19 +1521,28 @@
       <c r="O21">
         <v>6</v>
       </c>
+      <c r="P21" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>47</v>
+      </c>
       <c r="R21" t="s">
-        <v>30</v>
-      </c>
-      <c r="S21" t="s">
-        <v>57</v>
-      </c>
-      <c r="U21" t="s">
-        <v>35</v>
-      </c>
-      <c r="W21">
-        <v>3</v>
-      </c>
-      <c r="X21">
+        <v>45</v>
+      </c>
+      <c r="S21">
+        <v>3</v>
+      </c>
+      <c r="W21" t="s">
+        <v>34</v>
+      </c>
+      <c r="X21" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1368,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1380,19 +1566,19 @@
         <v>-31</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H22" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I22" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -1403,19 +1589,28 @@
       <c r="O22">
         <v>2</v>
       </c>
+      <c r="P22" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>47</v>
+      </c>
       <c r="R22" t="s">
-        <v>30</v>
-      </c>
-      <c r="S22" t="s">
-        <v>61</v>
-      </c>
-      <c r="U22" t="s">
-        <v>30</v>
-      </c>
-      <c r="W22">
-        <v>3</v>
-      </c>
-      <c r="X22">
+        <v>74</v>
+      </c>
+      <c r="S22">
+        <v>3</v>
+      </c>
+      <c r="W22" t="s">
+        <v>34</v>
+      </c>
+      <c r="X22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1427,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1439,39 +1634,45 @@
         <v>-31</v>
       </c>
       <c r="G23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" t="s">
         <v>35</v>
       </c>
-      <c r="H23" t="s">
-        <v>31</v>
-      </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J23">
         <v>-5</v>
       </c>
       <c r="K23" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L23">
         <v>6</v>
       </c>
       <c r="M23" t="s">
-        <v>29</v>
-      </c>
-      <c r="R23" t="s">
-        <v>30</v>
-      </c>
-      <c r="S23" t="s">
-        <v>62</v>
-      </c>
-      <c r="U23" t="s">
-        <v>30</v>
-      </c>
-      <c r="W23">
-        <v>3</v>
-      </c>
-      <c r="X23">
+        <v>33</v>
+      </c>
+      <c r="P23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>40</v>
+      </c>
+      <c r="S23">
+        <v>3</v>
+      </c>
+      <c r="W23" t="s">
+        <v>34</v>
+      </c>
+      <c r="X23" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1483,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1495,36 +1696,45 @@
         <v>-26</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I24" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J24">
         <v>-5</v>
       </c>
       <c r="K24" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L24">
         <v>7</v>
       </c>
+      <c r="P24" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>47</v>
+      </c>
       <c r="R24" t="s">
-        <v>30</v>
-      </c>
-      <c r="S24" t="s">
-        <v>57</v>
-      </c>
-      <c r="U24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W24">
-        <v>3</v>
-      </c>
-      <c r="X24">
+        <v>78</v>
+      </c>
+      <c r="S24">
+        <v>3</v>
+      </c>
+      <c r="W24" t="s">
+        <v>34</v>
+      </c>
+      <c r="X24" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1536,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>4</v>
@@ -1548,15 +1758,15 @@
         <v>-21</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I25" t="s">
-        <v>64</v>
-      </c>
-      <c r="X25">
+        <v>79</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1568,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1580,36 +1790,39 @@
         <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L26">
         <v>6</v>
       </c>
-      <c r="Q26">
+      <c r="P26" t="s">
+        <v>44</v>
+      </c>
+      <c r="V26">
         <v>0</v>
       </c>
-      <c r="R26" t="s">
-        <v>48</v>
-      </c>
-      <c r="S26" t="s">
-        <v>49</v>
-      </c>
-      <c r="U26" t="s">
-        <v>30</v>
-      </c>
-      <c r="X26">
+      <c r="W26" t="s">
+        <v>59</v>
+      </c>
+      <c r="X26" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1621,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1633,33 +1846,36 @@
         <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J27">
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L27">
         <v>5</v>
       </c>
-      <c r="R27" t="s">
-        <v>30</v>
-      </c>
-      <c r="S27" t="s">
-        <v>36</v>
-      </c>
-      <c r="U27" t="s">
-        <v>30</v>
-      </c>
-      <c r="X27">
+      <c r="P27" t="s">
+        <v>44</v>
+      </c>
+      <c r="W27" t="s">
+        <v>34</v>
+      </c>
+      <c r="X27" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1671,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -1683,19 +1899,19 @@
         <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I28" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -1706,16 +1922,19 @@
       <c r="O28">
         <v>7</v>
       </c>
-      <c r="R28" t="s">
-        <v>35</v>
-      </c>
-      <c r="S28" t="s">
-        <v>61</v>
-      </c>
-      <c r="U28" t="s">
-        <v>30</v>
-      </c>
-      <c r="X28">
+      <c r="P28" t="s">
+        <v>66</v>
+      </c>
+      <c r="W28" t="s">
+        <v>41</v>
+      </c>
+      <c r="X28" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1727,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -1739,15 +1958,15 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H29" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I29" t="s">
-        <v>66</v>
-      </c>
-      <c r="X29">
+        <v>81</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1759,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1771,36 +1990,42 @@
         <v>-20</v>
       </c>
       <c r="G30" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30" t="s">
-        <v>67</v>
-      </c>
-      <c r="R30" t="s">
-        <v>35</v>
-      </c>
-      <c r="U30" t="s">
-        <v>30</v>
-      </c>
-      <c r="W30">
-        <v>3</v>
-      </c>
-      <c r="X30">
+        <v>82</v>
+      </c>
+      <c r="P30" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>83</v>
+      </c>
+      <c r="S30">
+        <v>3</v>
+      </c>
+      <c r="W30" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB30">
         <v>3</v>
       </c>
     </row>
@@ -1812,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1824,19 +2049,19 @@
         <v>-19</v>
       </c>
       <c r="G31" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I31" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -1847,19 +2072,28 @@
       <c r="O31">
         <v>9</v>
       </c>
+      <c r="P31" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>47</v>
+      </c>
       <c r="R31" t="s">
-        <v>35</v>
-      </c>
-      <c r="S31" t="s">
-        <v>68</v>
-      </c>
-      <c r="U31" t="s">
-        <v>35</v>
-      </c>
-      <c r="W31">
-        <v>3</v>
-      </c>
-      <c r="X31">
+        <v>40</v>
+      </c>
+      <c r="S31">
+        <v>3</v>
+      </c>
+      <c r="W31" t="s">
+        <v>41</v>
+      </c>
+      <c r="X31" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB31">
         <v>3</v>
       </c>
     </row>
@@ -1871,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -1883,19 +2117,19 @@
         <v>-19</v>
       </c>
       <c r="G32" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H32" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J32">
         <v>29</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -1906,19 +2140,28 @@
       <c r="O32">
         <v>5</v>
       </c>
+      <c r="P32" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>47</v>
+      </c>
       <c r="R32" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" t="s">
-        <v>69</v>
-      </c>
-      <c r="U32" t="s">
-        <v>35</v>
-      </c>
-      <c r="W32">
-        <v>3</v>
-      </c>
-      <c r="X32">
+        <v>45</v>
+      </c>
+      <c r="S32">
+        <v>3</v>
+      </c>
+      <c r="W32" t="s">
+        <v>41</v>
+      </c>
+      <c r="X32" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB32">
         <v>3</v>
       </c>
     </row>
@@ -1930,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1942,39 +2185,45 @@
         <v>-48</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H33" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J33">
         <v>6</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L33">
         <v>7</v>
       </c>
       <c r="M33" t="s">
-        <v>34</v>
-      </c>
-      <c r="R33" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" t="s">
-        <v>70</v>
-      </c>
-      <c r="U33" t="s">
-        <v>35</v>
-      </c>
-      <c r="W33">
-        <v>3</v>
-      </c>
-      <c r="X33">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>88</v>
+      </c>
+      <c r="S33">
+        <v>3</v>
+      </c>
+      <c r="W33" t="s">
+        <v>41</v>
+      </c>
+      <c r="X33" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB33">
         <v>3</v>
       </c>
     </row>
@@ -1986,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1998,39 +2247,45 @@
         <v>47</v>
       </c>
       <c r="G34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" t="s">
         <v>35</v>
       </c>
-      <c r="H34" t="s">
-        <v>31</v>
-      </c>
       <c r="I34" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J34">
         <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L34">
         <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>67</v>
-      </c>
-      <c r="R34" t="s">
-        <v>30</v>
-      </c>
-      <c r="S34" t="s">
-        <v>62</v>
-      </c>
-      <c r="U34" t="s">
-        <v>35</v>
-      </c>
-      <c r="W34">
-        <v>3</v>
-      </c>
-      <c r="X34">
+        <v>82</v>
+      </c>
+      <c r="P34" t="s">
+        <v>29</v>
+      </c>
+      <c r="S34">
+        <v>3</v>
+      </c>
+      <c r="T34" t="s">
+        <v>50</v>
+      </c>
+      <c r="W34" t="s">
+        <v>34</v>
+      </c>
+      <c r="X34" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
     </row>
@@ -2042,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -2054,39 +2309,45 @@
         <v>43</v>
       </c>
       <c r="G35" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" t="s">
         <v>35</v>
       </c>
-      <c r="H35" t="s">
-        <v>31</v>
-      </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L35">
         <v>6</v>
       </c>
       <c r="M35" t="s">
-        <v>67</v>
-      </c>
-      <c r="R35" t="s">
-        <v>30</v>
-      </c>
-      <c r="S35" t="s">
-        <v>39</v>
-      </c>
-      <c r="U35" t="s">
-        <v>35</v>
-      </c>
-      <c r="W35">
-        <v>3</v>
-      </c>
-      <c r="X35">
+        <v>82</v>
+      </c>
+      <c r="P35" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>91</v>
+      </c>
+      <c r="S35">
+        <v>3</v>
+      </c>
+      <c r="W35" t="s">
+        <v>34</v>
+      </c>
+      <c r="X35" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -2098,7 +2359,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2110,19 +2371,19 @@
         <v>42</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H36" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I36" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L36">
         <v>7</v>
@@ -2133,19 +2394,28 @@
       <c r="O36">
         <v>8</v>
       </c>
-      <c r="R36" t="s">
-        <v>30</v>
-      </c>
-      <c r="S36" t="s">
-        <v>71</v>
-      </c>
-      <c r="U36" t="s">
-        <v>35</v>
-      </c>
-      <c r="W36">
-        <v>3</v>
-      </c>
-      <c r="X36">
+      <c r="P36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>47</v>
+      </c>
+      <c r="S36">
+        <v>3</v>
+      </c>
+      <c r="T36" t="s">
+        <v>50</v>
+      </c>
+      <c r="W36" t="s">
+        <v>34</v>
+      </c>
+      <c r="X36" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB36">
         <v>3</v>
       </c>
     </row>
@@ -2157,7 +2427,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -2169,39 +2439,48 @@
         <v>42</v>
       </c>
       <c r="G37" t="s">
+        <v>41</v>
+      </c>
+      <c r="H37" t="s">
         <v>35</v>
       </c>
-      <c r="H37" t="s">
-        <v>31</v>
-      </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L37">
         <v>6</v>
       </c>
       <c r="M37" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>93</v>
       </c>
       <c r="R37" t="s">
-        <v>30</v>
-      </c>
-      <c r="S37" t="s">
-        <v>54</v>
-      </c>
-      <c r="U37" t="s">
-        <v>35</v>
-      </c>
-      <c r="W37">
-        <v>3</v>
-      </c>
-      <c r="X37">
+        <v>40</v>
+      </c>
+      <c r="S37">
+        <v>3</v>
+      </c>
+      <c r="W37" t="s">
+        <v>34</v>
+      </c>
+      <c r="X37" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB37">
         <v>3</v>
       </c>
     </row>
@@ -2213,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -2225,19 +2504,19 @@
         <v>42</v>
       </c>
       <c r="G38" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H38" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I38" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J38">
         <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -2248,19 +2527,28 @@
       <c r="O38">
         <v>2</v>
       </c>
+      <c r="P38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>47</v>
+      </c>
       <c r="R38" t="s">
-        <v>30</v>
-      </c>
-      <c r="S38" t="s">
-        <v>61</v>
-      </c>
-      <c r="U38" t="s">
-        <v>35</v>
-      </c>
-      <c r="W38">
-        <v>6</v>
-      </c>
-      <c r="X38">
+        <v>94</v>
+      </c>
+      <c r="S38">
+        <v>6</v>
+      </c>
+      <c r="W38" t="s">
+        <v>34</v>
+      </c>
+      <c r="X38" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB38">
         <v>3</v>
       </c>
     </row>
@@ -2272,7 +2560,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2284,39 +2572,45 @@
         <v>29</v>
       </c>
       <c r="G39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H39" t="s">
         <v>35</v>
       </c>
-      <c r="H39" t="s">
-        <v>31</v>
-      </c>
       <c r="I39" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J39">
         <v>5</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L39">
         <v>8</v>
       </c>
       <c r="M39" t="s">
-        <v>29</v>
-      </c>
-      <c r="R39" t="s">
-        <v>30</v>
-      </c>
-      <c r="S39" t="s">
-        <v>71</v>
-      </c>
-      <c r="U39" t="s">
-        <v>30</v>
-      </c>
-      <c r="W39">
-        <v>3</v>
-      </c>
-      <c r="X39">
+        <v>33</v>
+      </c>
+      <c r="P39" t="s">
+        <v>44</v>
+      </c>
+      <c r="S39">
+        <v>3</v>
+      </c>
+      <c r="T39" t="s">
+        <v>95</v>
+      </c>
+      <c r="W39" t="s">
+        <v>34</v>
+      </c>
+      <c r="X39" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB39">
         <v>3</v>
       </c>
     </row>
@@ -2328,7 +2622,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2340,33 +2634,39 @@
         <v>24</v>
       </c>
       <c r="G40" t="s">
+        <v>41</v>
+      </c>
+      <c r="H40" t="s">
         <v>35</v>
       </c>
-      <c r="H40" t="s">
-        <v>31</v>
-      </c>
       <c r="I40" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J40">
         <v>5</v>
       </c>
       <c r="K40" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L40">
         <v>6</v>
       </c>
-      <c r="R40" t="s">
-        <v>30</v>
-      </c>
-      <c r="S40" t="s">
-        <v>41</v>
-      </c>
-      <c r="W40">
-        <v>3</v>
-      </c>
-      <c r="X40">
+      <c r="P40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>45</v>
+      </c>
+      <c r="S40">
+        <v>3</v>
+      </c>
+      <c r="W40" t="s">
+        <v>34</v>
+      </c>
+      <c r="X40" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
     </row>
@@ -2378,7 +2678,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2390,39 +2690,45 @@
         <v>19</v>
       </c>
       <c r="G41" t="s">
+        <v>41</v>
+      </c>
+      <c r="H41" t="s">
         <v>35</v>
       </c>
-      <c r="H41" t="s">
-        <v>31</v>
-      </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J41">
         <v>4</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L41">
         <v>7</v>
       </c>
       <c r="M41" t="s">
-        <v>29</v>
-      </c>
-      <c r="R41" t="s">
-        <v>30</v>
-      </c>
-      <c r="S41" t="s">
-        <v>53</v>
-      </c>
-      <c r="U41" t="s">
-        <v>30</v>
-      </c>
-      <c r="W41">
-        <v>3</v>
-      </c>
-      <c r="X41">
+        <v>33</v>
+      </c>
+      <c r="P41" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>74</v>
+      </c>
+      <c r="S41">
+        <v>3</v>
+      </c>
+      <c r="W41" t="s">
+        <v>34</v>
+      </c>
+      <c r="X41" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2434,7 +2740,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2446,19 +2752,19 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I42" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L42">
         <v>6</v>
@@ -2469,19 +2775,28 @@
       <c r="O42">
         <v>1</v>
       </c>
-      <c r="R42" t="s">
-        <v>48</v>
+      <c r="P42" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>47</v>
       </c>
       <c r="S42" t="s">
-        <v>73</v>
-      </c>
-      <c r="U42" t="s">
-        <v>30</v>
+        <v>98</v>
+      </c>
+      <c r="T42" t="s">
+        <v>99</v>
       </c>
       <c r="W42" t="s">
-        <v>74</v>
-      </c>
-      <c r="X42">
+        <v>34</v>
+      </c>
+      <c r="X42" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2493,7 +2808,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -2505,39 +2820,48 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I43" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J43">
         <v>6</v>
       </c>
       <c r="K43" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L43">
         <v>8</v>
       </c>
       <c r="M43" t="s">
-        <v>29</v>
-      </c>
-      <c r="R43" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="P43" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>47</v>
       </c>
       <c r="S43" t="s">
-        <v>41</v>
-      </c>
-      <c r="U43" t="s">
-        <v>30</v>
+        <v>53</v>
+      </c>
+      <c r="T43" t="s">
+        <v>54</v>
       </c>
       <c r="W43" t="s">
-        <v>44</v>
-      </c>
-      <c r="X43">
+        <v>41</v>
+      </c>
+      <c r="X43" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2549,7 +2873,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2561,36 +2885,39 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H44" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I44" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J44">
         <v>-2</v>
       </c>
       <c r="K44" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L44">
         <v>10</v>
       </c>
       <c r="M44" t="s">
-        <v>29</v>
-      </c>
-      <c r="R44" t="s">
-        <v>35</v>
-      </c>
-      <c r="U44" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="S44" t="s">
+        <v>98</v>
+      </c>
+      <c r="T44" t="s">
+        <v>99</v>
       </c>
       <c r="W44" t="s">
-        <v>74</v>
-      </c>
-      <c r="X44">
+        <v>41</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB44">
         <v>3</v>
       </c>
     </row>
@@ -2602,7 +2929,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -2614,19 +2941,19 @@
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I45" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L45">
         <v>7</v>
@@ -2637,19 +2964,28 @@
       <c r="O45">
         <v>4</v>
       </c>
-      <c r="R45" t="s">
-        <v>30</v>
-      </c>
-      <c r="S45" t="s">
-        <v>75</v>
-      </c>
-      <c r="U45" t="s">
-        <v>30</v>
-      </c>
-      <c r="W45">
-        <v>3</v>
-      </c>
-      <c r="X45">
+      <c r="P45" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>47</v>
+      </c>
+      <c r="S45">
+        <v>3</v>
+      </c>
+      <c r="T45" t="s">
+        <v>101</v>
+      </c>
+      <c r="W45" t="s">
+        <v>34</v>
+      </c>
+      <c r="X45" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB45">
         <v>3</v>
       </c>
     </row>
@@ -2661,7 +2997,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -2673,19 +3009,19 @@
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H46" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I46" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L46">
         <v>9</v>
@@ -2696,19 +3032,28 @@
       <c r="O46">
         <v>1</v>
       </c>
-      <c r="R46" t="s">
-        <v>30</v>
+      <c r="P46" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>47</v>
       </c>
       <c r="S46" t="s">
-        <v>57</v>
-      </c>
-      <c r="U46" t="s">
-        <v>30</v>
+        <v>98</v>
+      </c>
+      <c r="T46" t="s">
+        <v>99</v>
       </c>
       <c r="W46" t="s">
-        <v>74</v>
-      </c>
-      <c r="X46">
+        <v>34</v>
+      </c>
+      <c r="X46" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB46">
         <v>3</v>
       </c>
     </row>
@@ -2720,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -2732,15 +3077,15 @@
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I47" t="s">
-        <v>59</v>
-      </c>
-      <c r="X47">
+        <v>72</v>
+      </c>
+      <c r="AB47">
         <v>3</v>
       </c>
     </row>
@@ -2752,7 +3097,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2764,13 +3109,13 @@
         <v>-40</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I48" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49">
@@ -2781,7 +3126,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2793,33 +3138,36 @@
         <v>-20</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I49" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J49">
         <v>2</v>
       </c>
       <c r="K49" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L49">
         <v>7</v>
       </c>
-      <c r="R49" t="s">
-        <v>35</v>
-      </c>
-      <c r="S49" t="s">
-        <v>54</v>
-      </c>
-      <c r="U49" t="s">
-        <v>30</v>
-      </c>
-      <c r="X49">
+      <c r="P49" t="s">
+        <v>44</v>
+      </c>
+      <c r="W49" t="s">
+        <v>41</v>
+      </c>
+      <c r="X49" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB49">
         <v>3</v>
       </c>
     </row>
@@ -2831,7 +3179,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2843,19 +3191,19 @@
         <v>-22</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H50" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I50" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J50">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L50">
         <v>5</v>
@@ -2866,16 +3214,19 @@
       <c r="O50">
         <v>2</v>
       </c>
-      <c r="R50" t="s">
-        <v>35</v>
-      </c>
-      <c r="S50" t="s">
-        <v>69</v>
-      </c>
-      <c r="U50" t="s">
-        <v>35</v>
-      </c>
-      <c r="X50">
+      <c r="P50" t="s">
+        <v>85</v>
+      </c>
+      <c r="W50" t="s">
+        <v>41</v>
+      </c>
+      <c r="X50" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB50">
         <v>3</v>
       </c>
     </row>
@@ -2887,7 +3238,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2899,33 +3250,36 @@
         <v>-29</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I51" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L51">
         <v>8</v>
       </c>
-      <c r="R51" t="s">
-        <v>48</v>
-      </c>
-      <c r="S51" t="s">
-        <v>79</v>
-      </c>
-      <c r="U51" t="s">
-        <v>35</v>
-      </c>
-      <c r="X51">
+      <c r="P51" t="s">
+        <v>44</v>
+      </c>
+      <c r="W51" t="s">
+        <v>59</v>
+      </c>
+      <c r="X51" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB51">
         <v>3</v>
       </c>
     </row>
@@ -2937,7 +3291,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D52">
         <v>4</v>
@@ -2949,15 +3303,15 @@
         <v>-29</v>
       </c>
       <c r="G52" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H52" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="I52" t="s">
-        <v>81</v>
-      </c>
-      <c r="X52">
+        <v>108</v>
+      </c>
+      <c r="AB52">
         <v>3</v>
       </c>
     </row>
@@ -2969,7 +3323,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2981,36 +3335,42 @@
         <v>-42</v>
       </c>
       <c r="G53" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H53" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J53">
         <v>14</v>
       </c>
       <c r="K53" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L53">
         <v>6</v>
       </c>
       <c r="M53" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q53">
+        <v>33</v>
+      </c>
+      <c r="P53" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>40</v>
+      </c>
+      <c r="S53">
+        <v>3</v>
+      </c>
+      <c r="V53">
         <v>0</v>
       </c>
-      <c r="U53" t="s">
-        <v>35</v>
-      </c>
-      <c r="W53">
-        <v>3</v>
-      </c>
-      <c r="X53">
+      <c r="Z53" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB53">
         <v>4</v>
       </c>
     </row>
@@ -3022,7 +3382,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3034,36 +3394,42 @@
         <v>44</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J54">
         <v>3</v>
       </c>
       <c r="K54" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L54">
         <v>7</v>
       </c>
       <c r="M54" t="s">
-        <v>40</v>
-      </c>
-      <c r="R54" t="s">
-        <v>35</v>
-      </c>
-      <c r="S54" t="s">
-        <v>75</v>
-      </c>
-      <c r="U54" t="s">
-        <v>30</v>
-      </c>
-      <c r="X54">
+        <v>49</v>
+      </c>
+      <c r="P54" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>47</v>
+      </c>
+      <c r="W54" t="s">
+        <v>41</v>
+      </c>
+      <c r="X54" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB54">
         <v>4</v>
       </c>
     </row>
@@ -3075,7 +3441,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -3087,39 +3453,45 @@
         <v>41</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H55" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I55" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J55">
         <v>3</v>
       </c>
       <c r="K55" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L55">
         <v>7</v>
       </c>
       <c r="M55" t="s">
-        <v>29</v>
-      </c>
-      <c r="R55" t="s">
-        <v>35</v>
-      </c>
-      <c r="S55" t="s">
-        <v>82</v>
-      </c>
-      <c r="U55" t="s">
-        <v>35</v>
-      </c>
-      <c r="W55">
-        <v>3</v>
-      </c>
-      <c r="X55">
+        <v>33</v>
+      </c>
+      <c r="P55" t="s">
+        <v>97</v>
+      </c>
+      <c r="S55">
+        <v>3</v>
+      </c>
+      <c r="T55" t="s">
+        <v>101</v>
+      </c>
+      <c r="W55" t="s">
+        <v>41</v>
+      </c>
+      <c r="X55" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB55">
         <v>4</v>
       </c>
     </row>
@@ -3131,7 +3503,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -3143,19 +3515,19 @@
         <v>38</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H56" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I56" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -3166,19 +3538,28 @@
       <c r="O56">
         <v>3</v>
       </c>
+      <c r="P56" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>47</v>
+      </c>
       <c r="R56" t="s">
-        <v>30</v>
-      </c>
-      <c r="S56" t="s">
-        <v>36</v>
-      </c>
-      <c r="U56" t="s">
-        <v>35</v>
-      </c>
-      <c r="W56">
-        <v>3</v>
-      </c>
-      <c r="X56">
+        <v>74</v>
+      </c>
+      <c r="S56">
+        <v>3</v>
+      </c>
+      <c r="W56" t="s">
+        <v>34</v>
+      </c>
+      <c r="X56" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB56">
         <v>4</v>
       </c>
     </row>
@@ -3190,7 +3571,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -3202,19 +3583,19 @@
         <v>38</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H57" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I57" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J57">
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L57">
         <v>6</v>
@@ -3225,19 +3606,25 @@
       <c r="O57">
         <v>2</v>
       </c>
-      <c r="R57" t="s">
-        <v>30</v>
-      </c>
-      <c r="S57" t="s">
-        <v>54</v>
-      </c>
-      <c r="U57" t="s">
-        <v>30</v>
-      </c>
-      <c r="W57">
-        <v>3</v>
-      </c>
-      <c r="X57">
+      <c r="P57" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>91</v>
+      </c>
+      <c r="S57">
+        <v>3</v>
+      </c>
+      <c r="W57" t="s">
+        <v>34</v>
+      </c>
+      <c r="X57" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB57">
         <v>4</v>
       </c>
     </row>
@@ -3249,7 +3636,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3261,39 +3648,45 @@
         <v>29</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H58" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I58" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J58">
         <v>10</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L58">
         <v>6</v>
       </c>
       <c r="M58" t="s">
-        <v>29</v>
-      </c>
-      <c r="R58" t="s">
-        <v>35</v>
-      </c>
-      <c r="S58" t="s">
-        <v>41</v>
-      </c>
-      <c r="U58" t="s">
-        <v>30</v>
-      </c>
-      <c r="W58">
-        <v>3</v>
-      </c>
-      <c r="X58">
+        <v>33</v>
+      </c>
+      <c r="P58" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>47</v>
+      </c>
+      <c r="S58">
+        <v>3</v>
+      </c>
+      <c r="W58" t="s">
+        <v>41</v>
+      </c>
+      <c r="X58" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB58">
         <v>4</v>
       </c>
     </row>
@@ -3305,7 +3698,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3317,39 +3710,45 @@
         <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H59" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J59">
         <v>10</v>
       </c>
       <c r="K59" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L59">
         <v>6</v>
       </c>
       <c r="M59" t="s">
-        <v>34</v>
-      </c>
-      <c r="R59" t="s">
-        <v>35</v>
-      </c>
-      <c r="S59" t="s">
-        <v>62</v>
-      </c>
-      <c r="U59" t="s">
-        <v>30</v>
-      </c>
-      <c r="W59">
-        <v>3</v>
-      </c>
-      <c r="X59">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>39</v>
+      </c>
+      <c r="S59">
+        <v>3</v>
+      </c>
+      <c r="T59" t="s">
+        <v>101</v>
+      </c>
+      <c r="W59" t="s">
+        <v>41</v>
+      </c>
+      <c r="X59" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
     </row>
@@ -3361,7 +3760,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3373,39 +3772,45 @@
         <v>9</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H60" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J60">
         <v>8</v>
       </c>
       <c r="K60" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L60">
         <v>8</v>
       </c>
       <c r="M60" t="s">
-        <v>29</v>
-      </c>
-      <c r="R60" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="P60" t="s">
+        <v>39</v>
       </c>
       <c r="S60" t="s">
-        <v>62</v>
-      </c>
-      <c r="U60" t="s">
-        <v>35</v>
+        <v>98</v>
+      </c>
+      <c r="T60" t="s">
+        <v>99</v>
       </c>
       <c r="W60" t="s">
-        <v>74</v>
-      </c>
-      <c r="X60">
+        <v>41</v>
+      </c>
+      <c r="X60" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB60">
         <v>4</v>
       </c>
     </row>
@@ -3417,7 +3822,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -3429,39 +3834,45 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L61">
         <v>9</v>
       </c>
       <c r="M61" t="s">
-        <v>29</v>
-      </c>
-      <c r="R61" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="P61" t="s">
+        <v>44</v>
       </c>
       <c r="S61" t="s">
-        <v>83</v>
-      </c>
-      <c r="U61" t="s">
-        <v>30</v>
+        <v>98</v>
+      </c>
+      <c r="T61" t="s">
+        <v>99</v>
       </c>
       <c r="W61" t="s">
-        <v>74</v>
-      </c>
-      <c r="X61">
+        <v>34</v>
+      </c>
+      <c r="X61" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB61">
         <v>4</v>
       </c>
     </row>
@@ -3473,7 +3884,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3485,15 +3896,15 @@
         <v>3</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="I62" t="s">
-        <v>59</v>
-      </c>
-      <c r="X62">
+        <v>72</v>
+      </c>
+      <c r="AB62">
         <v>4</v>
       </c>
     </row>
@@ -3505,7 +3916,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3517,13 +3928,13 @@
         <v>-40</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H63" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I63" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64">
@@ -3534,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3546,33 +3957,36 @@
         <v>-20</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L64">
         <v>6</v>
       </c>
-      <c r="R64" t="s">
-        <v>48</v>
-      </c>
-      <c r="S64" t="s">
-        <v>49</v>
-      </c>
-      <c r="U64" t="s">
-        <v>30</v>
-      </c>
-      <c r="X64">
+      <c r="P64" t="s">
+        <v>44</v>
+      </c>
+      <c r="W64" t="s">
+        <v>59</v>
+      </c>
+      <c r="X64" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB64">
         <v>4</v>
       </c>
     </row>
@@ -3584,7 +3998,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3596,33 +4010,36 @@
         <v>-25</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H65" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J65">
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L65">
         <v>6</v>
       </c>
-      <c r="R65" t="s">
-        <v>48</v>
-      </c>
-      <c r="S65" t="s">
-        <v>49</v>
-      </c>
-      <c r="U65" t="s">
-        <v>30</v>
-      </c>
-      <c r="X65">
+      <c r="P65" t="s">
+        <v>44</v>
+      </c>
+      <c r="W65" t="s">
+        <v>59</v>
+      </c>
+      <c r="X65" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB65">
         <v>4</v>
       </c>
     </row>
@@ -3634,7 +4051,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -3646,33 +4063,36 @@
         <v>-29</v>
       </c>
       <c r="G66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J66">
         <v>3</v>
       </c>
       <c r="K66" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L66">
         <v>6</v>
       </c>
-      <c r="R66" t="s">
-        <v>48</v>
-      </c>
-      <c r="S66" t="s">
-        <v>49</v>
-      </c>
-      <c r="U66" t="s">
-        <v>35</v>
-      </c>
-      <c r="X66">
+      <c r="P66" t="s">
+        <v>44</v>
+      </c>
+      <c r="W66" t="s">
+        <v>59</v>
+      </c>
+      <c r="X66" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB66">
         <v>4</v>
       </c>
     </row>
@@ -3684,7 +4104,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3696,33 +4116,36 @@
         <v>-32</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I67" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="J67">
         <v>14</v>
       </c>
       <c r="K67" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L67">
         <v>6</v>
       </c>
-      <c r="R67" t="s">
-        <v>48</v>
-      </c>
-      <c r="S67" t="s">
-        <v>49</v>
-      </c>
-      <c r="U67" t="s">
-        <v>30</v>
-      </c>
-      <c r="X67">
+      <c r="P67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W67" t="s">
+        <v>59</v>
+      </c>
+      <c r="X67" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB67">
         <v>4</v>
       </c>
     </row>
@@ -3734,7 +4157,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3746,33 +4169,36 @@
         <v>-46</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H68" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J68">
         <v>16</v>
       </c>
       <c r="K68" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L68">
         <v>6</v>
       </c>
-      <c r="R68" t="s">
-        <v>48</v>
-      </c>
-      <c r="S68" t="s">
-        <v>49</v>
-      </c>
-      <c r="U68" t="s">
-        <v>30</v>
-      </c>
-      <c r="X68">
+      <c r="P68" t="s">
+        <v>44</v>
+      </c>
+      <c r="W68" t="s">
+        <v>59</v>
+      </c>
+      <c r="X68" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB68">
         <v>4</v>
       </c>
     </row>
@@ -3784,7 +4210,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -3796,33 +4222,36 @@
         <v>38</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H69" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I69" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J69">
         <v>-3</v>
       </c>
       <c r="K69" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L69">
         <v>6</v>
       </c>
-      <c r="R69" t="s">
-        <v>48</v>
-      </c>
-      <c r="S69" t="s">
-        <v>49</v>
-      </c>
-      <c r="U69" t="s">
-        <v>30</v>
-      </c>
-      <c r="X69">
+      <c r="P69" t="s">
+        <v>44</v>
+      </c>
+      <c r="W69" t="s">
+        <v>59</v>
+      </c>
+      <c r="X69" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB69">
         <v>4</v>
       </c>
     </row>
@@ -3834,7 +4263,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -3846,19 +4275,19 @@
         <v>41</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H70" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I70" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="J70">
         <v>41</v>
       </c>
       <c r="K70" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L70">
         <v>6</v>
@@ -3869,16 +4298,19 @@
       <c r="O70">
         <v>7</v>
       </c>
-      <c r="R70" t="s">
-        <v>35</v>
-      </c>
-      <c r="S70" t="s">
-        <v>55</v>
-      </c>
-      <c r="U70" t="s">
-        <v>30</v>
-      </c>
-      <c r="X70">
+      <c r="P70" t="s">
+        <v>66</v>
+      </c>
+      <c r="W70" t="s">
+        <v>41</v>
+      </c>
+      <c r="X70" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB70">
         <v>4</v>
       </c>
     </row>
@@ -3890,7 +4322,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3902,15 +4334,15 @@
         <v>3</v>
       </c>
       <c r="G71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I71" t="s">
-        <v>59</v>
-      </c>
-      <c r="X71">
+        <v>72</v>
+      </c>
+      <c r="AB71">
         <v>4</v>
       </c>
     </row>
@@ -3922,7 +4354,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3934,13 +4366,13 @@
         <v>-40</v>
       </c>
       <c r="G72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H72" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I72" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73">
@@ -3951,7 +4383,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3963,39 +4395,42 @@
         <v>-20</v>
       </c>
       <c r="G73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H73" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J73">
         <v>8</v>
       </c>
       <c r="K73" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L73">
         <v>7</v>
       </c>
       <c r="M73" t="s">
-        <v>40</v>
-      </c>
-      <c r="R73" t="s">
-        <v>35</v>
-      </c>
-      <c r="S73" t="s">
-        <v>53</v>
-      </c>
-      <c r="U73" t="s">
-        <v>30</v>
-      </c>
-      <c r="W73">
-        <v>3</v>
-      </c>
-      <c r="X73">
+        <v>49</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>47</v>
+      </c>
+      <c r="S73">
+        <v>3</v>
+      </c>
+      <c r="W73" t="s">
+        <v>41</v>
+      </c>
+      <c r="X73" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB73">
         <v>5</v>
       </c>
     </row>
@@ -4007,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -4019,39 +4454,45 @@
         <v>-28</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J74">
         <v>3</v>
       </c>
       <c r="K74" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L74">
         <v>7</v>
       </c>
       <c r="M74" t="s">
-        <v>34</v>
-      </c>
-      <c r="R74" t="s">
-        <v>35</v>
-      </c>
-      <c r="S74" t="s">
-        <v>87</v>
-      </c>
-      <c r="U74" t="s">
-        <v>35</v>
-      </c>
-      <c r="W74">
-        <v>3</v>
-      </c>
-      <c r="X74">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>47</v>
+      </c>
+      <c r="S74">
+        <v>3</v>
+      </c>
+      <c r="W74" t="s">
+        <v>41</v>
+      </c>
+      <c r="X74" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB74">
         <v>5</v>
       </c>
     </row>
@@ -4063,7 +4504,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -4075,39 +4516,45 @@
         <v>-31</v>
       </c>
       <c r="G75" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J75">
         <v>14</v>
       </c>
       <c r="K75" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L75">
         <v>7</v>
       </c>
       <c r="M75" t="s">
-        <v>37</v>
-      </c>
-      <c r="R75" t="s">
-        <v>35</v>
-      </c>
-      <c r="S75" t="s">
-        <v>41</v>
-      </c>
-      <c r="U75" t="s">
-        <v>30</v>
-      </c>
-      <c r="W75">
-        <v>3</v>
-      </c>
-      <c r="X75">
+        <v>43</v>
+      </c>
+      <c r="P75" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>47</v>
+      </c>
+      <c r="S75">
+        <v>3</v>
+      </c>
+      <c r="W75" t="s">
+        <v>41</v>
+      </c>
+      <c r="X75" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -4119,7 +4566,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -4131,15 +4578,15 @@
         <v>-40</v>
       </c>
       <c r="G76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H76" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I76" t="s">
-        <v>28</v>
-      </c>
-      <c r="X76">
+        <v>32</v>
+      </c>
+      <c r="AB76">
         <v>5</v>
       </c>
     </row>
@@ -4151,7 +4598,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -4163,33 +4610,36 @@
         <v>-20</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H77" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J77">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L77">
         <v>6</v>
       </c>
-      <c r="R77" t="s">
-        <v>48</v>
-      </c>
-      <c r="S77" t="s">
-        <v>49</v>
-      </c>
-      <c r="U77" t="s">
-        <v>30</v>
-      </c>
-      <c r="X77">
+      <c r="P77" t="s">
+        <v>44</v>
+      </c>
+      <c r="W77" t="s">
+        <v>59</v>
+      </c>
+      <c r="X77" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB77">
         <v>4</v>
       </c>
     </row>
@@ -4201,7 +4651,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -4213,33 +4663,36 @@
         <v>-21</v>
       </c>
       <c r="G78" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J78">
         <v>5</v>
       </c>
       <c r="K78" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L78">
         <v>6</v>
       </c>
-      <c r="R78" t="s">
-        <v>35</v>
-      </c>
-      <c r="S78" t="s">
-        <v>53</v>
-      </c>
-      <c r="U78" t="s">
-        <v>35</v>
-      </c>
-      <c r="X78">
+      <c r="P78" t="s">
+        <v>115</v>
+      </c>
+      <c r="W78" t="s">
+        <v>41</v>
+      </c>
+      <c r="X78" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB78">
         <v>4</v>
       </c>
     </row>
@@ -4251,7 +4704,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D79">
         <v>3</v>
@@ -4263,33 +4716,36 @@
         <v>-26</v>
       </c>
       <c r="G79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J79">
         <v>-5</v>
       </c>
       <c r="K79" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L79">
         <v>6</v>
       </c>
-      <c r="R79" t="s">
-        <v>48</v>
-      </c>
-      <c r="S79" t="s">
-        <v>49</v>
-      </c>
-      <c r="U79" t="s">
-        <v>35</v>
-      </c>
-      <c r="X79">
+      <c r="P79" t="s">
+        <v>44</v>
+      </c>
+      <c r="W79" t="s">
+        <v>59</v>
+      </c>
+      <c r="X79" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB79">
         <v>4</v>
       </c>
     </row>
@@ -4301,7 +4757,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -4313,15 +4769,15 @@
         <v>-21</v>
       </c>
       <c r="G80" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H80" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="I80" t="s">
-        <v>46</v>
-      </c>
-      <c r="X80">
+        <v>57</v>
+      </c>
+      <c r="AB80">
         <v>4</v>
       </c>
     </row>
@@ -4333,7 +4789,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -4345,39 +4801,45 @@
         <v>-45</v>
       </c>
       <c r="G81" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J81">
         <v>-2</v>
       </c>
       <c r="K81" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L81">
         <v>7</v>
       </c>
       <c r="M81" t="s">
-        <v>29</v>
-      </c>
-      <c r="R81" t="s">
-        <v>48</v>
-      </c>
-      <c r="S81" t="s">
-        <v>88</v>
-      </c>
-      <c r="U81" t="s">
-        <v>30</v>
-      </c>
-      <c r="W81">
-        <v>3</v>
-      </c>
-      <c r="X81">
+        <v>33</v>
+      </c>
+      <c r="P81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>47</v>
+      </c>
+      <c r="S81">
+        <v>3</v>
+      </c>
+      <c r="W81" t="s">
+        <v>59</v>
+      </c>
+      <c r="X81" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB81">
         <v>6</v>
       </c>
     </row>
@@ -4389,7 +4851,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -4401,19 +4863,19 @@
         <v>-43</v>
       </c>
       <c r="G82" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H82" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I82" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L82">
         <v>6</v>
@@ -4424,19 +4886,25 @@
       <c r="O82">
         <v>5</v>
       </c>
-      <c r="R82" t="s">
-        <v>48</v>
-      </c>
-      <c r="S82" t="s">
-        <v>49</v>
-      </c>
-      <c r="U82" t="s">
-        <v>35</v>
-      </c>
-      <c r="W82">
-        <v>3</v>
-      </c>
-      <c r="X82">
+      <c r="P82" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>91</v>
+      </c>
+      <c r="S82">
+        <v>3</v>
+      </c>
+      <c r="W82" t="s">
+        <v>34</v>
+      </c>
+      <c r="X82" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB82">
         <v>6</v>
       </c>
     </row>
@@ -4448,7 +4916,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -4460,19 +4928,19 @@
         <v>-43</v>
       </c>
       <c r="G83" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H83" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I83" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J83">
         <v>19</v>
       </c>
       <c r="K83" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L83">
         <v>6</v>
@@ -4483,19 +4951,28 @@
       <c r="O83">
         <v>5</v>
       </c>
+      <c r="P83" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>47</v>
+      </c>
       <c r="R83" t="s">
-        <v>30</v>
-      </c>
-      <c r="S83" t="s">
-        <v>61</v>
-      </c>
-      <c r="U83" t="s">
-        <v>30</v>
-      </c>
-      <c r="W83">
-        <v>3</v>
-      </c>
-      <c r="X83">
+        <v>88</v>
+      </c>
+      <c r="S83">
+        <v>3</v>
+      </c>
+      <c r="W83" t="s">
+        <v>34</v>
+      </c>
+      <c r="X83" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB83">
         <v>6</v>
       </c>
     </row>
@@ -4507,7 +4984,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -4519,19 +4996,19 @@
         <v>38</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H84" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I84" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J84">
         <v>20</v>
       </c>
       <c r="K84" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L84">
         <v>8</v>
@@ -4542,19 +5019,28 @@
       <c r="O84">
         <v>4</v>
       </c>
-      <c r="R84" t="s">
-        <v>30</v>
+      <c r="P84" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>47</v>
       </c>
       <c r="S84" t="s">
-        <v>55</v>
-      </c>
-      <c r="U84" t="s">
-        <v>30</v>
+        <v>53</v>
+      </c>
+      <c r="T84" t="s">
+        <v>117</v>
       </c>
       <c r="W84" t="s">
-        <v>44</v>
-      </c>
-      <c r="X84">
+        <v>34</v>
+      </c>
+      <c r="X84" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB84">
         <v>6</v>
       </c>
     </row>
@@ -4566,7 +5052,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -4578,39 +5064,45 @@
         <v>18</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H85" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J85">
         <v>18</v>
       </c>
       <c r="K85" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L85">
         <v>7</v>
       </c>
       <c r="M85" t="s">
-        <v>40</v>
-      </c>
-      <c r="R85" t="s">
-        <v>35</v>
-      </c>
-      <c r="S85" t="s">
-        <v>41</v>
-      </c>
-      <c r="U85" t="s">
-        <v>30</v>
-      </c>
-      <c r="W85">
-        <v>3</v>
-      </c>
-      <c r="X85">
+        <v>49</v>
+      </c>
+      <c r="P85" t="s">
+        <v>87</v>
+      </c>
+      <c r="S85">
+        <v>3</v>
+      </c>
+      <c r="T85" t="s">
+        <v>101</v>
+      </c>
+      <c r="W85" t="s">
+        <v>41</v>
+      </c>
+      <c r="X85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB85">
         <v>6</v>
       </c>
     </row>
@@ -4622,7 +5114,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -4634,15 +5126,15 @@
         <v>3</v>
       </c>
       <c r="G86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H86" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="I86" t="s">
-        <v>59</v>
-      </c>
-      <c r="X86">
+        <v>72</v>
+      </c>
+      <c r="AB86">
         <v>6</v>
       </c>
     </row>
@@ -4654,7 +5146,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4666,13 +5158,13 @@
         <v>-40</v>
       </c>
       <c r="G87" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H87" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I87" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -4683,7 +5175,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4695,19 +5187,19 @@
         <v>-20</v>
       </c>
       <c r="G88" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H88" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I88" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L88">
         <v>6</v>
@@ -4718,16 +5210,19 @@
       <c r="O88">
         <v>9</v>
       </c>
-      <c r="R88" t="s">
-        <v>48</v>
-      </c>
-      <c r="S88" t="s">
-        <v>49</v>
-      </c>
-      <c r="U88" t="s">
-        <v>35</v>
-      </c>
-      <c r="X88">
+      <c r="P88" t="s">
+        <v>44</v>
+      </c>
+      <c r="W88" t="s">
+        <v>59</v>
+      </c>
+      <c r="X88" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB88">
         <v>5</v>
       </c>
     </row>
@@ -4739,7 +5234,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4751,33 +5246,36 @@
         <v>-20</v>
       </c>
       <c r="G89" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H89" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I89" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="J89">
         <v>9</v>
       </c>
       <c r="K89" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L89">
         <v>6</v>
       </c>
-      <c r="R89" t="s">
-        <v>35</v>
-      </c>
-      <c r="S89" t="s">
-        <v>61</v>
-      </c>
-      <c r="U89" t="s">
-        <v>30</v>
-      </c>
-      <c r="X89">
+      <c r="P89" t="s">
+        <v>39</v>
+      </c>
+      <c r="W89" t="s">
+        <v>41</v>
+      </c>
+      <c r="X89" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB89">
         <v>5</v>
       </c>
     </row>
@@ -4789,7 +5287,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -4801,33 +5299,36 @@
         <v>-29</v>
       </c>
       <c r="G90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H90" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J90">
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L90">
         <v>8</v>
       </c>
-      <c r="R90" t="s">
-        <v>35</v>
-      </c>
-      <c r="S90" t="s">
-        <v>70</v>
-      </c>
-      <c r="U90" t="s">
-        <v>35</v>
-      </c>
-      <c r="X90">
+      <c r="P90" t="s">
+        <v>44</v>
+      </c>
+      <c r="W90" t="s">
+        <v>41</v>
+      </c>
+      <c r="X90" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB90">
         <v>5</v>
       </c>
     </row>
@@ -4839,7 +5340,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4851,33 +5352,36 @@
         <v>-31</v>
       </c>
       <c r="G91" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J91">
         <v>5</v>
       </c>
       <c r="K91" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L91">
         <v>6</v>
       </c>
-      <c r="R91" t="s">
-        <v>48</v>
-      </c>
-      <c r="S91" t="s">
-        <v>49</v>
-      </c>
-      <c r="U91" t="s">
-        <v>30</v>
-      </c>
-      <c r="X91">
+      <c r="P91" t="s">
+        <v>44</v>
+      </c>
+      <c r="W91" t="s">
+        <v>59</v>
+      </c>
+      <c r="X91" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB91">
         <v>5</v>
       </c>
     </row>
@@ -4889,7 +5393,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -4901,39 +5405,42 @@
         <v>-36</v>
       </c>
       <c r="G92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H92" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I92" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J92">
         <v>7</v>
       </c>
       <c r="K92" t="s">
+        <v>52</v>
+      </c>
+      <c r="L92">
+        <v>6</v>
+      </c>
+      <c r="N92">
+        <v>6</v>
+      </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="P92" t="s">
+        <v>66</v>
+      </c>
+      <c r="W92" t="s">
+        <v>41</v>
+      </c>
+      <c r="X92" t="s">
         <v>42</v>
       </c>
-      <c r="L92">
-        <v>6</v>
-      </c>
-      <c r="N92">
-        <v>6</v>
-      </c>
-      <c r="O92">
-        <v>1</v>
-      </c>
-      <c r="R92" t="s">
-        <v>35</v>
-      </c>
-      <c r="S92" t="s">
-        <v>36</v>
-      </c>
-      <c r="U92" t="s">
-        <v>30</v>
-      </c>
-      <c r="X92">
+      <c r="Z92" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB92">
         <v>5</v>
       </c>
     </row>
@@ -4945,7 +5452,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4957,19 +5464,19 @@
         <v>-43</v>
       </c>
       <c r="G93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H93" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I93" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J93">
         <v>18</v>
       </c>
       <c r="K93" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L93">
         <v>5</v>
@@ -4980,16 +5487,19 @@
       <c r="O93">
         <v>2</v>
       </c>
-      <c r="R93" t="s">
-        <v>35</v>
-      </c>
-      <c r="S93" t="s">
-        <v>55</v>
-      </c>
-      <c r="U93" t="s">
-        <v>35</v>
-      </c>
-      <c r="X93">
+      <c r="P93" t="s">
+        <v>44</v>
+      </c>
+      <c r="W93" t="s">
+        <v>41</v>
+      </c>
+      <c r="X93" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB93">
         <v>5</v>
       </c>
     </row>
@@ -5001,7 +5511,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -5013,19 +5523,19 @@
         <v>39</v>
       </c>
       <c r="G94" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H94" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I94" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L94">
         <v>7</v>
@@ -5036,16 +5546,19 @@
       <c r="O94">
         <v>7</v>
       </c>
-      <c r="R94" t="s">
-        <v>48</v>
-      </c>
-      <c r="S94" t="s">
-        <v>49</v>
-      </c>
-      <c r="U94" t="s">
-        <v>30</v>
-      </c>
-      <c r="X94">
+      <c r="P94" t="s">
+        <v>44</v>
+      </c>
+      <c r="W94" t="s">
+        <v>59</v>
+      </c>
+      <c r="X94" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB94">
         <v>5</v>
       </c>
     </row>
@@ -5057,7 +5570,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D95">
         <v>2</v>
@@ -5069,33 +5582,36 @@
         <v>39</v>
       </c>
       <c r="G95" t="s">
+        <v>41</v>
+      </c>
+      <c r="H95" t="s">
         <v>35</v>
       </c>
-      <c r="H95" t="s">
-        <v>31</v>
-      </c>
       <c r="I95" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L95">
         <v>5</v>
       </c>
-      <c r="R95" t="s">
-        <v>48</v>
-      </c>
-      <c r="S95" t="s">
-        <v>49</v>
-      </c>
-      <c r="U95" t="s">
-        <v>30</v>
-      </c>
-      <c r="X95">
+      <c r="P95" t="s">
+        <v>44</v>
+      </c>
+      <c r="W95" t="s">
+        <v>59</v>
+      </c>
+      <c r="X95" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB95">
         <v>5</v>
       </c>
     </row>
@@ -5107,7 +5623,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -5119,19 +5635,19 @@
         <v>39</v>
       </c>
       <c r="G96" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H96" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I96" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L96">
         <v>6</v>
@@ -5142,16 +5658,19 @@
       <c r="O96">
         <v>6</v>
       </c>
-      <c r="R96" t="s">
-        <v>35</v>
-      </c>
-      <c r="S96" t="s">
-        <v>55</v>
-      </c>
-      <c r="U96" t="s">
-        <v>35</v>
-      </c>
-      <c r="X96">
+      <c r="P96" t="s">
+        <v>44</v>
+      </c>
+      <c r="W96" t="s">
+        <v>41</v>
+      </c>
+      <c r="X96" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB96">
         <v>5</v>
       </c>
     </row>
@@ -5163,7 +5682,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D97">
         <v>4</v>
@@ -5175,18 +5694,18 @@
         <v>39</v>
       </c>
       <c r="G97" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H97" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="I97" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J97">
         <v>-5</v>
       </c>
-      <c r="X97">
+      <c r="AB97">
         <v>5</v>
       </c>
     </row>
@@ -5198,7 +5717,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D98">
         <v>4</v>
@@ -5210,15 +5729,15 @@
         <v>44</v>
       </c>
       <c r="G98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H98" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="I98" t="s">
-        <v>81</v>
-      </c>
-      <c r="X98">
+        <v>108</v>
+      </c>
+      <c r="AB98">
         <v>7</v>
       </c>
     </row>
@@ -5230,7 +5749,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -5242,42 +5761,48 @@
         <v>-10</v>
       </c>
       <c r="G99" t="s">
+        <v>41</v>
+      </c>
+      <c r="H99" t="s">
         <v>35</v>
       </c>
-      <c r="H99" t="s">
-        <v>31</v>
-      </c>
       <c r="I99" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J99">
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L99">
         <v>6</v>
       </c>
       <c r="M99" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q99">
+        <v>33</v>
+      </c>
+      <c r="P99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>40</v>
+      </c>
+      <c r="S99">
+        <v>3</v>
+      </c>
+      <c r="V99">
         <v>0</v>
       </c>
-      <c r="R99" t="s">
-        <v>30</v>
-      </c>
-      <c r="S99" t="s">
-        <v>62</v>
-      </c>
-      <c r="U99" t="s">
-        <v>30</v>
-      </c>
-      <c r="W99">
-        <v>3</v>
-      </c>
-      <c r="X99">
+      <c r="W99" t="s">
+        <v>34</v>
+      </c>
+      <c r="X99" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB99">
         <v>6</v>
       </c>
     </row>
@@ -5289,7 +5814,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -5301,39 +5826,45 @@
         <v>-12</v>
       </c>
       <c r="G100" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H100" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I100" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J100">
         <v>17</v>
       </c>
       <c r="K100" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L100">
         <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>67</v>
-      </c>
-      <c r="R100" t="s">
-        <v>35</v>
+        <v>82</v>
+      </c>
+      <c r="P100" t="s">
+        <v>39</v>
       </c>
       <c r="S100" t="s">
-        <v>61</v>
-      </c>
-      <c r="U100" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="T100" t="s">
+        <v>118</v>
       </c>
       <c r="W100" t="s">
-        <v>44</v>
-      </c>
-      <c r="X100">
+        <v>41</v>
+      </c>
+      <c r="X100" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB100">
         <v>6</v>
       </c>
     </row>
@@ -5345,7 +5876,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -5357,39 +5888,45 @@
         <v>-29</v>
       </c>
       <c r="G101" t="s">
+        <v>41</v>
+      </c>
+      <c r="H101" t="s">
         <v>35</v>
       </c>
-      <c r="H101" t="s">
-        <v>31</v>
-      </c>
       <c r="I101" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J101">
         <v>11</v>
       </c>
       <c r="K101" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L101">
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>40</v>
-      </c>
-      <c r="R101" t="s">
-        <v>30</v>
-      </c>
-      <c r="S101" t="s">
-        <v>57</v>
-      </c>
-      <c r="U101" t="s">
-        <v>35</v>
-      </c>
-      <c r="W101">
-        <v>3</v>
-      </c>
-      <c r="X101">
+        <v>49</v>
+      </c>
+      <c r="P101" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>45</v>
+      </c>
+      <c r="S101">
+        <v>3</v>
+      </c>
+      <c r="W101" t="s">
+        <v>34</v>
+      </c>
+      <c r="X101" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB101">
         <v>6</v>
       </c>
     </row>
@@ -5401,7 +5938,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -5413,39 +5950,45 @@
         <v>-40</v>
       </c>
       <c r="G102" t="s">
+        <v>41</v>
+      </c>
+      <c r="H102" t="s">
         <v>35</v>
       </c>
-      <c r="H102" t="s">
-        <v>31</v>
-      </c>
       <c r="I102" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L102">
         <v>7</v>
       </c>
       <c r="M102" t="s">
-        <v>40</v>
-      </c>
-      <c r="R102" t="s">
-        <v>30</v>
+        <v>49</v>
+      </c>
+      <c r="P102" t="s">
+        <v>39</v>
       </c>
       <c r="S102" t="s">
-        <v>89</v>
-      </c>
-      <c r="U102" t="s">
-        <v>30</v>
+        <v>53</v>
+      </c>
+      <c r="T102" t="s">
+        <v>54</v>
       </c>
       <c r="W102" t="s">
-        <v>44</v>
-      </c>
-      <c r="X102">
+        <v>34</v>
+      </c>
+      <c r="X102" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB102">
         <v>6</v>
       </c>
     </row>
@@ -5457,7 +6000,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -5469,19 +6012,19 @@
         <v>-40</v>
       </c>
       <c r="G103" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H103" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I103" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J103">
         <v>12</v>
       </c>
       <c r="K103" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L103">
         <v>6</v>
@@ -5492,19 +6035,28 @@
       <c r="O103">
         <v>1</v>
       </c>
+      <c r="P103" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>47</v>
+      </c>
       <c r="R103" t="s">
-        <v>30</v>
-      </c>
-      <c r="S103" t="s">
-        <v>89</v>
-      </c>
-      <c r="U103" t="s">
-        <v>30</v>
-      </c>
-      <c r="W103">
-        <v>3</v>
-      </c>
-      <c r="X103">
+        <v>74</v>
+      </c>
+      <c r="S103">
+        <v>3</v>
+      </c>
+      <c r="W103" t="s">
+        <v>34</v>
+      </c>
+      <c r="X103" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB103">
         <v>6</v>
       </c>
     </row>
@@ -5516,7 +6068,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -5528,39 +6080,45 @@
         <v>48</v>
       </c>
       <c r="G104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I104" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L104">
         <v>6</v>
       </c>
       <c r="M104" t="s">
-        <v>40</v>
-      </c>
-      <c r="R104" t="s">
-        <v>35</v>
-      </c>
-      <c r="S104" t="s">
-        <v>62</v>
-      </c>
-      <c r="U104" t="s">
-        <v>35</v>
-      </c>
-      <c r="W104">
-        <v>3</v>
-      </c>
-      <c r="X104">
+        <v>49</v>
+      </c>
+      <c r="P104" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>93</v>
+      </c>
+      <c r="S104">
+        <v>3</v>
+      </c>
+      <c r="W104" t="s">
+        <v>41</v>
+      </c>
+      <c r="X104" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB104">
         <v>6</v>
       </c>
     </row>
@@ -5572,7 +6130,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5584,19 +6142,19 @@
         <v>48</v>
       </c>
       <c r="G105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H105" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I105" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J105">
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L105">
         <v>6</v>
@@ -5607,19 +6165,25 @@
       <c r="O105">
         <v>1</v>
       </c>
-      <c r="R105" t="s">
-        <v>48</v>
+      <c r="P105" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>47</v>
       </c>
       <c r="S105" t="s">
-        <v>73</v>
-      </c>
-      <c r="U105" t="s">
-        <v>30</v>
-      </c>
-      <c r="W105">
-        <v>3</v>
-      </c>
-      <c r="X105">
+        <v>53</v>
+      </c>
+      <c r="W105" t="s">
+        <v>34</v>
+      </c>
+      <c r="X105" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB105">
         <v>6</v>
       </c>
     </row>
@@ -5631,7 +6195,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -5643,19 +6207,19 @@
         <v>46</v>
       </c>
       <c r="G106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H106" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I106" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L106">
         <v>6</v>
@@ -5666,19 +6230,28 @@
       <c r="O106">
         <v>9</v>
       </c>
+      <c r="P106" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>47</v>
+      </c>
       <c r="R106" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="S106" t="s">
-        <v>68</v>
-      </c>
-      <c r="U106" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W106" t="s">
-        <v>44</v>
-      </c>
-      <c r="X106">
+        <v>41</v>
+      </c>
+      <c r="X106" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB106">
         <v>6</v>
       </c>
     </row>
@@ -5690,7 +6263,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D107">
         <v>4</v>
@@ -5702,21 +6275,21 @@
         <v>46</v>
       </c>
       <c r="G107" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H107" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J107">
         <v>14</v>
       </c>
-      <c r="U107" t="s">
-        <v>35</v>
-      </c>
-      <c r="X107">
+      <c r="Z107" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB107">
         <v>6</v>
       </c>
     </row>
@@ -5728,7 +6301,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5740,39 +6313,45 @@
         <v>32</v>
       </c>
       <c r="G108" t="s">
+        <v>41</v>
+      </c>
+      <c r="H108" t="s">
         <v>35</v>
       </c>
-      <c r="H108" t="s">
-        <v>31</v>
-      </c>
       <c r="I108" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J108">
         <v>-1</v>
       </c>
       <c r="K108" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L108">
         <v>8</v>
       </c>
       <c r="M108" t="s">
-        <v>67</v>
-      </c>
-      <c r="R108" t="s">
-        <v>48</v>
-      </c>
-      <c r="S108" t="s">
-        <v>88</v>
-      </c>
-      <c r="U108" t="s">
-        <v>35</v>
-      </c>
-      <c r="W108">
-        <v>3</v>
-      </c>
-      <c r="X108">
+        <v>82</v>
+      </c>
+      <c r="P108" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>47</v>
+      </c>
+      <c r="S108">
+        <v>3</v>
+      </c>
+      <c r="W108" t="s">
+        <v>59</v>
+      </c>
+      <c r="X108" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB108">
         <v>6</v>
       </c>
     </row>
@@ -5784,7 +6363,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -5796,19 +6375,19 @@
         <v>33</v>
       </c>
       <c r="G109" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H109" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I109" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J109">
         <v>15</v>
       </c>
       <c r="K109" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L109">
         <v>6</v>
@@ -5819,16 +6398,25 @@
       <c r="O109">
         <v>2</v>
       </c>
-      <c r="R109" t="s">
-        <v>30</v>
-      </c>
-      <c r="U109" t="s">
-        <v>30</v>
+      <c r="P109" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>47</v>
+      </c>
+      <c r="S109" t="s">
+        <v>53</v>
+      </c>
+      <c r="T109" t="s">
+        <v>118</v>
       </c>
       <c r="W109" t="s">
-        <v>44</v>
-      </c>
-      <c r="X109">
+        <v>34</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB109">
         <v>6</v>
       </c>
     </row>
@@ -5840,7 +6428,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -5852,39 +6440,42 @@
         <v>18</v>
       </c>
       <c r="G110" t="s">
+        <v>41</v>
+      </c>
+      <c r="H110" t="s">
         <v>35</v>
       </c>
-      <c r="H110" t="s">
-        <v>31</v>
-      </c>
       <c r="I110" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J110">
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L110">
         <v>8</v>
       </c>
       <c r="M110" t="s">
-        <v>40</v>
-      </c>
-      <c r="R110" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="S110" t="s">
-        <v>82</v>
-      </c>
-      <c r="U110" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="T110" t="s">
+        <v>54</v>
       </c>
       <c r="W110" t="s">
-        <v>44</v>
-      </c>
-      <c r="X110">
+        <v>34</v>
+      </c>
+      <c r="X110" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB110">
         <v>6</v>
       </c>
     </row>
@@ -5896,7 +6487,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -5908,39 +6499,42 @@
         <v>17</v>
       </c>
       <c r="G111" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H111" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I111" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J111">
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L111">
         <v>7</v>
       </c>
       <c r="M111" t="s">
-        <v>40</v>
-      </c>
-      <c r="R111" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="S111" t="s">
         <v>53</v>
       </c>
-      <c r="U111" t="s">
-        <v>30</v>
+      <c r="T111" t="s">
+        <v>122</v>
       </c>
       <c r="W111" t="s">
-        <v>44</v>
-      </c>
-      <c r="X111">
+        <v>41</v>
+      </c>
+      <c r="X111" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB111">
         <v>6</v>
       </c>
     </row>
@@ -5952,7 +6546,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -5964,39 +6558,45 @@
         <v>16</v>
       </c>
       <c r="G112" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H112" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I112" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J112">
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L112">
         <v>7</v>
       </c>
       <c r="M112" t="s">
-        <v>40</v>
-      </c>
-      <c r="R112" t="s">
-        <v>30</v>
+        <v>49</v>
+      </c>
+      <c r="P112" t="s">
+        <v>123</v>
       </c>
       <c r="S112" t="s">
-        <v>57</v>
-      </c>
-      <c r="U112" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="T112" t="s">
+        <v>124</v>
       </c>
       <c r="W112" t="s">
-        <v>44</v>
-      </c>
-      <c r="X112">
+        <v>34</v>
+      </c>
+      <c r="X112" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB112">
         <v>6</v>
       </c>
     </row>
@@ -6008,7 +6608,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>3</v>
@@ -6020,39 +6620,45 @@
         <v>15</v>
       </c>
       <c r="G113" t="s">
+        <v>41</v>
+      </c>
+      <c r="H113" t="s">
         <v>35</v>
       </c>
-      <c r="H113" t="s">
-        <v>31</v>
-      </c>
       <c r="I113" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J113">
         <v>4</v>
       </c>
       <c r="K113" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L113">
         <v>6</v>
       </c>
       <c r="M113" t="s">
-        <v>67</v>
-      </c>
-      <c r="R113" t="s">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="P113" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>40</v>
       </c>
       <c r="S113" t="s">
-        <v>57</v>
-      </c>
-      <c r="U113" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W113" t="s">
-        <v>44</v>
-      </c>
-      <c r="X113">
+        <v>34</v>
+      </c>
+      <c r="X113" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB113">
         <v>6</v>
       </c>
     </row>
@@ -6064,7 +6670,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -6076,15 +6682,15 @@
         <v>11</v>
       </c>
       <c r="G114" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H114" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I114" t="s">
-        <v>59</v>
-      </c>
-      <c r="X114">
+        <v>72</v>
+      </c>
+      <c r="AB114">
         <v>6</v>
       </c>
     </row>
@@ -6096,7 +6702,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -6108,15 +6714,15 @@
         <v>-40</v>
       </c>
       <c r="G115" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H115" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I115" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q115">
+        <v>105</v>
+      </c>
+      <c r="V115">
         <v>5</v>
       </c>
     </row>
@@ -6128,7 +6734,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -6140,33 +6746,36 @@
         <v>-19</v>
       </c>
       <c r="G116" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H116" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I116" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J116">
         <v>7</v>
       </c>
       <c r="K116" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L116">
         <v>6</v>
       </c>
-      <c r="R116" t="s">
-        <v>48</v>
-      </c>
-      <c r="S116" t="s">
-        <v>49</v>
-      </c>
-      <c r="U116" t="s">
-        <v>30</v>
-      </c>
-      <c r="X116">
+      <c r="P116" t="s">
+        <v>44</v>
+      </c>
+      <c r="W116" t="s">
+        <v>59</v>
+      </c>
+      <c r="X116" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB116">
         <v>8</v>
       </c>
     </row>
@@ -6178,7 +6787,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -6190,19 +6799,19 @@
         <v>-27</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H117" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I117" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L117">
         <v>6</v>
@@ -6213,16 +6822,19 @@
       <c r="O117">
         <v>2</v>
       </c>
-      <c r="R117" t="s">
-        <v>48</v>
-      </c>
-      <c r="S117" t="s">
-        <v>49</v>
-      </c>
-      <c r="U117" t="s">
-        <v>35</v>
-      </c>
-      <c r="X117">
+      <c r="P117" t="s">
+        <v>44</v>
+      </c>
+      <c r="W117" t="s">
+        <v>59</v>
+      </c>
+      <c r="X117" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB117">
         <v>8</v>
       </c>
     </row>
@@ -6234,7 +6846,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D118">
         <v>3</v>
@@ -6246,19 +6858,19 @@
         <v>-27</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H118" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I118" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J118">
         <v>17</v>
       </c>
       <c r="K118" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L118">
         <v>6</v>
@@ -6269,16 +6881,19 @@
       <c r="O118">
         <v>2</v>
       </c>
-      <c r="R118" t="s">
-        <v>35</v>
-      </c>
-      <c r="S118" t="s">
-        <v>36</v>
-      </c>
-      <c r="U118" t="s">
-        <v>35</v>
-      </c>
-      <c r="X118">
+      <c r="P118" t="s">
+        <v>66</v>
+      </c>
+      <c r="W118" t="s">
+        <v>41</v>
+      </c>
+      <c r="X118" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB118">
         <v>8</v>
       </c>
     </row>
@@ -6290,7 +6905,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -6302,19 +6917,19 @@
         <v>-44</v>
       </c>
       <c r="G119" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H119" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I119" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L119">
         <v>5</v>
@@ -6325,16 +6940,19 @@
       <c r="O119">
         <v>3</v>
       </c>
-      <c r="R119" t="s">
-        <v>30</v>
-      </c>
-      <c r="S119" t="s">
-        <v>55</v>
-      </c>
-      <c r="U119" t="s">
-        <v>35</v>
-      </c>
-      <c r="X119">
+      <c r="P119" t="s">
+        <v>39</v>
+      </c>
+      <c r="W119" t="s">
+        <v>34</v>
+      </c>
+      <c r="X119" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB119">
         <v>8</v>
       </c>
     </row>
@@ -6346,7 +6964,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -6358,33 +6976,36 @@
         <v>-44</v>
       </c>
       <c r="G120" t="s">
+        <v>41</v>
+      </c>
+      <c r="H120" t="s">
         <v>35</v>
       </c>
-      <c r="H120" t="s">
-        <v>31</v>
-      </c>
       <c r="I120" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J120">
         <v>16</v>
       </c>
       <c r="K120" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L120">
         <v>5</v>
       </c>
-      <c r="R120" t="s">
-        <v>48</v>
-      </c>
-      <c r="S120" t="s">
-        <v>49</v>
-      </c>
-      <c r="U120" t="s">
-        <v>35</v>
-      </c>
-      <c r="X120">
+      <c r="P120" t="s">
+        <v>44</v>
+      </c>
+      <c r="W120" t="s">
+        <v>59</v>
+      </c>
+      <c r="X120" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB120">
         <v>8</v>
       </c>
     </row>
@@ -6396,7 +7017,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -6408,33 +7029,36 @@
         <v>40</v>
       </c>
       <c r="G121" t="s">
+        <v>41</v>
+      </c>
+      <c r="H121" t="s">
         <v>35</v>
       </c>
-      <c r="H121" t="s">
-        <v>31</v>
-      </c>
       <c r="I121" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J121">
         <v>3</v>
       </c>
       <c r="K121" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L121">
         <v>6</v>
       </c>
-      <c r="R121" t="s">
-        <v>30</v>
-      </c>
-      <c r="S121" t="s">
-        <v>70</v>
-      </c>
-      <c r="U121" t="s">
-        <v>30</v>
-      </c>
-      <c r="X121">
+      <c r="P121" t="s">
+        <v>44</v>
+      </c>
+      <c r="W121" t="s">
+        <v>34</v>
+      </c>
+      <c r="X121" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB121">
         <v>8</v>
       </c>
     </row>
@@ -6446,7 +7070,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -6458,33 +7082,36 @@
         <v>37</v>
       </c>
       <c r="G122" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H122" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I122" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J122">
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L122">
         <v>7</v>
       </c>
-      <c r="R122" t="s">
-        <v>48</v>
-      </c>
-      <c r="S122" t="s">
-        <v>49</v>
-      </c>
-      <c r="U122" t="s">
-        <v>30</v>
-      </c>
-      <c r="X122">
+      <c r="P122" t="s">
+        <v>44</v>
+      </c>
+      <c r="W122" t="s">
+        <v>59</v>
+      </c>
+      <c r="X122" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB122">
         <v>8</v>
       </c>
     </row>
@@ -6496,7 +7123,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -6508,19 +7135,19 @@
         <v>35</v>
       </c>
       <c r="G123" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H123" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I123" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J123">
         <v>15</v>
       </c>
       <c r="K123" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L123">
         <v>5</v>
@@ -6531,16 +7158,19 @@
       <c r="O123">
         <v>7</v>
       </c>
-      <c r="R123" t="s">
-        <v>35</v>
-      </c>
-      <c r="S123" t="s">
-        <v>61</v>
-      </c>
-      <c r="U123" t="s">
-        <v>30</v>
-      </c>
-      <c r="X123">
+      <c r="P123" t="s">
+        <v>66</v>
+      </c>
+      <c r="W123" t="s">
+        <v>41</v>
+      </c>
+      <c r="X123" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB123">
         <v>8</v>
       </c>
     </row>
@@ -6552,7 +7182,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -6564,33 +7194,36 @@
         <v>20</v>
       </c>
       <c r="G124" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H124" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I124" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J124">
         <v>8</v>
       </c>
       <c r="K124" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L124">
         <v>7</v>
       </c>
-      <c r="R124" t="s">
-        <v>35</v>
-      </c>
-      <c r="S124" t="s">
-        <v>75</v>
-      </c>
-      <c r="U124" t="s">
-        <v>35</v>
-      </c>
-      <c r="X124">
+      <c r="P124" t="s">
+        <v>44</v>
+      </c>
+      <c r="W124" t="s">
+        <v>41</v>
+      </c>
+      <c r="X124" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB124">
         <v>8</v>
       </c>
     </row>
@@ -6602,7 +7235,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -6614,19 +7247,19 @@
         <v>12</v>
       </c>
       <c r="G125" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H125" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I125" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="J125">
         <v>12</v>
       </c>
       <c r="K125" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L125">
         <v>7</v>
@@ -6637,16 +7270,16 @@
       <c r="O125">
         <v>5</v>
       </c>
-      <c r="R125" t="s">
-        <v>30</v>
-      </c>
-      <c r="S125" t="s">
-        <v>53</v>
-      </c>
-      <c r="U125" t="s">
-        <v>30</v>
-      </c>
-      <c r="X125">
+      <c r="W125" t="s">
+        <v>34</v>
+      </c>
+      <c r="X125" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB125">
         <v>8</v>
       </c>
     </row>
@@ -6658,7 +7291,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -6670,15 +7303,15 @@
         <v>3</v>
       </c>
       <c r="G126" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H126" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I126" t="s">
-        <v>59</v>
-      </c>
-      <c r="X126">
+        <v>72</v>
+      </c>
+      <c r="AB126">
         <v>8</v>
       </c>
     </row>
@@ -6690,7 +7323,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -6702,13 +7335,13 @@
         <v>-40</v>
       </c>
       <c r="G127" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H127" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I127" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128">
@@ -6719,7 +7352,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -6731,39 +7364,45 @@
         <v>-20</v>
       </c>
       <c r="G128" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H128" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I128" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J128">
         <v>3</v>
       </c>
       <c r="K128" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L128">
         <v>7</v>
       </c>
       <c r="M128" t="s">
-        <v>67</v>
-      </c>
-      <c r="R128" t="s">
-        <v>35</v>
-      </c>
-      <c r="S128" t="s">
-        <v>70</v>
-      </c>
-      <c r="U128" t="s">
-        <v>30</v>
-      </c>
-      <c r="W128">
-        <v>3</v>
-      </c>
-      <c r="X128">
+        <v>82</v>
+      </c>
+      <c r="P128" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>93</v>
+      </c>
+      <c r="S128">
+        <v>3</v>
+      </c>
+      <c r="W128" t="s">
+        <v>41</v>
+      </c>
+      <c r="X128" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB128">
         <v>7</v>
       </c>
     </row>
@@ -6775,7 +7414,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D129">
         <v>2</v>
@@ -6787,19 +7426,19 @@
         <v>-23</v>
       </c>
       <c r="G129" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H129" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I129" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="J129">
         <v>3</v>
       </c>
       <c r="K129" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L129">
         <v>7</v>
@@ -6810,19 +7449,28 @@
       <c r="O129">
         <v>3</v>
       </c>
+      <c r="P129" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>47</v>
+      </c>
       <c r="R129" t="s">
-        <v>35</v>
-      </c>
-      <c r="S129" t="s">
-        <v>62</v>
-      </c>
-      <c r="U129" t="s">
-        <v>35</v>
-      </c>
-      <c r="W129">
-        <v>3</v>
-      </c>
-      <c r="X129">
+        <v>40</v>
+      </c>
+      <c r="S129">
+        <v>3</v>
+      </c>
+      <c r="W129" t="s">
+        <v>41</v>
+      </c>
+      <c r="X129" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB129">
         <v>7</v>
       </c>
     </row>
@@ -6834,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -6846,33 +7494,36 @@
         <v>31</v>
       </c>
       <c r="G130" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H130" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I130" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J130">
         <v>17</v>
       </c>
       <c r="K130" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L130">
         <v>6</v>
       </c>
-      <c r="R130" t="s">
-        <v>48</v>
-      </c>
-      <c r="S130" t="s">
-        <v>49</v>
-      </c>
-      <c r="U130" t="s">
-        <v>35</v>
-      </c>
-      <c r="X130">
+      <c r="P130" t="s">
+        <v>44</v>
+      </c>
+      <c r="W130" t="s">
+        <v>59</v>
+      </c>
+      <c r="X130" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB130">
         <v>9</v>
       </c>
     </row>
@@ -6884,7 +7535,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -6896,33 +7547,36 @@
         <v>14</v>
       </c>
       <c r="G131" t="s">
+        <v>41</v>
+      </c>
+      <c r="H131" t="s">
         <v>35</v>
       </c>
-      <c r="H131" t="s">
-        <v>31</v>
-      </c>
       <c r="I131" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J131">
         <v>10</v>
       </c>
       <c r="K131" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L131">
         <v>6</v>
       </c>
-      <c r="R131" t="s">
-        <v>48</v>
-      </c>
-      <c r="S131" t="s">
-        <v>49</v>
-      </c>
-      <c r="U131" t="s">
-        <v>35</v>
-      </c>
-      <c r="X131">
+      <c r="P131" t="s">
+        <v>44</v>
+      </c>
+      <c r="W131" t="s">
+        <v>59</v>
+      </c>
+      <c r="X131" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB131">
         <v>9</v>
       </c>
     </row>
@@ -6934,7 +7588,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -6946,33 +7600,36 @@
         <v>4</v>
       </c>
       <c r="G132" t="s">
+        <v>41</v>
+      </c>
+      <c r="H132" t="s">
         <v>35</v>
       </c>
-      <c r="H132" t="s">
-        <v>31</v>
-      </c>
       <c r="I132" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J132">
         <v>4</v>
       </c>
       <c r="K132" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L132">
         <v>7</v>
       </c>
-      <c r="R132" t="s">
-        <v>48</v>
-      </c>
-      <c r="S132" t="s">
-        <v>49</v>
-      </c>
-      <c r="U132" t="s">
-        <v>35</v>
-      </c>
-      <c r="X132">
+      <c r="P132" t="s">
+        <v>44</v>
+      </c>
+      <c r="W132" t="s">
+        <v>59</v>
+      </c>
+      <c r="X132" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB132">
         <v>9</v>
       </c>
     </row>
@@ -6984,7 +7641,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -6996,15 +7653,15 @@
         <v>3</v>
       </c>
       <c r="G133" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H133" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I133" t="s">
-        <v>59</v>
-      </c>
-      <c r="X133">
+        <v>72</v>
+      </c>
+      <c r="AB133">
         <v>9</v>
       </c>
     </row>
@@ -7016,7 +7673,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -7028,13 +7685,13 @@
         <v>-40</v>
       </c>
       <c r="G134" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H134" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I134" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135">
@@ -7045,7 +7702,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -7057,39 +7714,45 @@
         <v>-20</v>
       </c>
       <c r="G135" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H135" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I135" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J135">
         <v>9</v>
       </c>
       <c r="K135" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L135">
         <v>7</v>
       </c>
       <c r="M135" t="s">
-        <v>29</v>
-      </c>
-      <c r="R135" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="P135" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>40</v>
       </c>
       <c r="S135" t="s">
-        <v>41</v>
-      </c>
-      <c r="U135" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W135" t="s">
-        <v>44</v>
-      </c>
-      <c r="X135">
+        <v>34</v>
+      </c>
+      <c r="X135" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB135">
         <v>8</v>
       </c>
     </row>
@@ -7101,7 +7764,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -7113,39 +7776,45 @@
         <v>-29</v>
       </c>
       <c r="G136" t="s">
+        <v>41</v>
+      </c>
+      <c r="H136" t="s">
         <v>35</v>
       </c>
-      <c r="H136" t="s">
-        <v>31</v>
-      </c>
       <c r="I136" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J136">
         <v>4</v>
       </c>
       <c r="K136" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L136">
         <v>7</v>
       </c>
       <c r="M136" t="s">
-        <v>29</v>
-      </c>
-      <c r="R136" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="P136" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>47</v>
       </c>
       <c r="S136" t="s">
-        <v>41</v>
-      </c>
-      <c r="U136" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W136" t="s">
-        <v>44</v>
-      </c>
-      <c r="X136">
+        <v>34</v>
+      </c>
+      <c r="X136" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB136">
         <v>8</v>
       </c>
     </row>
@@ -7157,7 +7826,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -7169,19 +7838,19 @@
         <v>-33</v>
       </c>
       <c r="G137" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H137" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I137" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J137">
         <v>15</v>
       </c>
       <c r="K137" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L137">
         <v>7</v>
@@ -7192,19 +7861,28 @@
       <c r="O137">
         <v>8</v>
       </c>
-      <c r="R137" t="s">
-        <v>30</v>
+      <c r="P137" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>47</v>
       </c>
       <c r="S137" t="s">
-        <v>36</v>
-      </c>
-      <c r="U137" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="T137" t="s">
+        <v>122</v>
       </c>
       <c r="W137" t="s">
-        <v>44</v>
-      </c>
-      <c r="X137">
+        <v>34</v>
+      </c>
+      <c r="X137" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB137">
         <v>8</v>
       </c>
     </row>
@@ -7216,7 +7894,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -7228,39 +7906,45 @@
         <v>-48</v>
       </c>
       <c r="G138" t="s">
+        <v>41</v>
+      </c>
+      <c r="H138" t="s">
         <v>35</v>
       </c>
-      <c r="H138" t="s">
-        <v>31</v>
-      </c>
       <c r="I138" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J138">
         <v>52</v>
       </c>
       <c r="K138" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L138">
         <v>7</v>
       </c>
       <c r="M138" t="s">
-        <v>40</v>
-      </c>
-      <c r="R138" t="s">
-        <v>35</v>
+        <v>49</v>
+      </c>
+      <c r="P138" t="s">
+        <v>39</v>
       </c>
       <c r="S138" t="s">
-        <v>75</v>
-      </c>
-      <c r="U138" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="T138" t="s">
+        <v>122</v>
       </c>
       <c r="W138" t="s">
-        <v>44</v>
-      </c>
-      <c r="X138">
+        <v>41</v>
+      </c>
+      <c r="X138" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB138">
         <v>8</v>
       </c>
     </row>
@@ -7272,7 +7956,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -7284,18 +7968,18 @@
         <v>3</v>
       </c>
       <c r="G139" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H139" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="I139" t="s">
-        <v>59</v>
-      </c>
-      <c r="U139" t="s">
-        <v>35</v>
-      </c>
-      <c r="X139">
+        <v>72</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB139">
         <v>8</v>
       </c>
     </row>
@@ -7307,7 +7991,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -7319,13 +8003,13 @@
         <v>-40</v>
       </c>
       <c r="G140" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H140" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I140" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
     </row>
     <row r="141">
@@ -7336,7 +8020,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -7348,19 +8032,19 @@
         <v>-25</v>
       </c>
       <c r="G141" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H141" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I141" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L141">
         <v>7</v>
@@ -7371,19 +8055,22 @@
       <c r="O141">
         <v>9</v>
       </c>
-      <c r="Q141">
+      <c r="P141" t="s">
+        <v>66</v>
+      </c>
+      <c r="V141">
         <v>0</v>
       </c>
-      <c r="R141" t="s">
-        <v>35</v>
-      </c>
-      <c r="S141" t="s">
-        <v>75</v>
-      </c>
-      <c r="U141" t="s">
-        <v>35</v>
-      </c>
-      <c r="X141">
+      <c r="W141" t="s">
+        <v>41</v>
+      </c>
+      <c r="X141" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB141">
         <v>10</v>
       </c>
     </row>
@@ -7395,7 +8082,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D142">
         <v>2</v>
@@ -7407,24 +8094,24 @@
         <v>-25</v>
       </c>
       <c r="G142" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H142" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I142" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L142">
         <v>5</v>
       </c>
-      <c r="X142">
+      <c r="AB142">
         <v>10</v>
       </c>
     </row>
@@ -7436,7 +8123,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D143">
         <v>3</v>
@@ -7448,19 +8135,19 @@
         <v>-25</v>
       </c>
       <c r="G143" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H143" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I143" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L143">
         <v>6</v>
@@ -7471,16 +8158,19 @@
       <c r="O143">
         <v>4</v>
       </c>
-      <c r="R143" t="s">
-        <v>35</v>
-      </c>
-      <c r="S143" t="s">
-        <v>36</v>
-      </c>
-      <c r="U143" t="s">
-        <v>30</v>
-      </c>
-      <c r="X143">
+      <c r="P143" t="s">
+        <v>66</v>
+      </c>
+      <c r="W143" t="s">
+        <v>41</v>
+      </c>
+      <c r="X143" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB143">
         <v>10</v>
       </c>
     </row>
@@ -7492,7 +8182,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D144">
         <v>4</v>
@@ -7504,15 +8194,15 @@
         <v>-25</v>
       </c>
       <c r="G144" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H144" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="I144" t="s">
-        <v>46</v>
-      </c>
-      <c r="X144">
+        <v>57</v>
+      </c>
+      <c r="AB144">
         <v>10</v>
       </c>
     </row>
@@ -7524,7 +8214,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -7536,39 +8226,45 @@
         <v>-17</v>
       </c>
       <c r="G145" t="s">
+        <v>41</v>
+      </c>
+      <c r="H145" t="s">
         <v>35</v>
       </c>
-      <c r="H145" t="s">
-        <v>31</v>
-      </c>
       <c r="I145" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J145">
         <v>1</v>
       </c>
       <c r="K145" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L145">
         <v>7</v>
       </c>
       <c r="M145" t="s">
-        <v>29</v>
-      </c>
-      <c r="R145" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="P145" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>40</v>
       </c>
       <c r="S145" t="s">
-        <v>41</v>
-      </c>
-      <c r="U145" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W145" t="s">
-        <v>44</v>
-      </c>
-      <c r="X145">
+        <v>34</v>
+      </c>
+      <c r="X145" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB145">
         <v>9</v>
       </c>
     </row>
@@ -7580,7 +8276,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -7592,39 +8288,45 @@
         <v>-18</v>
       </c>
       <c r="G146" t="s">
+        <v>41</v>
+      </c>
+      <c r="H146" t="s">
         <v>35</v>
       </c>
-      <c r="H146" t="s">
-        <v>31</v>
-      </c>
       <c r="I146" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J146">
         <v>15</v>
       </c>
       <c r="K146" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L146">
         <v>8</v>
       </c>
       <c r="M146" t="s">
-        <v>67</v>
-      </c>
-      <c r="R146" t="s">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="P146" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>45</v>
       </c>
       <c r="S146" t="s">
         <v>53</v>
       </c>
-      <c r="U146" t="s">
-        <v>30</v>
-      </c>
       <c r="W146" t="s">
-        <v>44</v>
-      </c>
-      <c r="X146">
+        <v>34</v>
+      </c>
+      <c r="X146" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z146" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB146">
         <v>9</v>
       </c>
     </row>
@@ -7636,7 +8338,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -7648,39 +8350,45 @@
         <v>-33</v>
       </c>
       <c r="G147" t="s">
+        <v>41</v>
+      </c>
+      <c r="H147" t="s">
         <v>35</v>
       </c>
-      <c r="H147" t="s">
-        <v>31</v>
-      </c>
       <c r="I147" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J147">
         <v>-2</v>
       </c>
       <c r="K147" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L147">
         <v>8</v>
       </c>
       <c r="M147" t="s">
-        <v>67</v>
-      </c>
-      <c r="R147" t="s">
-        <v>35</v>
+        <v>82</v>
+      </c>
+      <c r="P147" t="s">
+        <v>29</v>
       </c>
       <c r="S147" t="s">
-        <v>57</v>
-      </c>
-      <c r="U147" t="s">
-        <v>30</v>
+        <v>53</v>
+      </c>
+      <c r="T147" t="s">
+        <v>54</v>
       </c>
       <c r="W147" t="s">
-        <v>44</v>
-      </c>
-      <c r="X147">
+        <v>41</v>
+      </c>
+      <c r="X147" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB147">
         <v>9</v>
       </c>
     </row>
@@ -7692,7 +8400,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D148">
         <v>2</v>
@@ -7704,19 +8412,19 @@
         <v>-31</v>
       </c>
       <c r="G148" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H148" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I148" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L148">
         <v>7</v>
@@ -7727,19 +8435,28 @@
       <c r="O148">
         <v>5</v>
       </c>
+      <c r="P148" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>47</v>
+      </c>
       <c r="R148" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S148" t="s">
-        <v>57</v>
-      </c>
-      <c r="U148" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W148" t="s">
-        <v>44</v>
-      </c>
-      <c r="X148">
+        <v>41</v>
+      </c>
+      <c r="X148" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB148">
         <v>9</v>
       </c>
     </row>
@@ -7751,7 +8468,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -7763,19 +8480,19 @@
         <v>-31</v>
       </c>
       <c r="G149" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H149" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I149" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J149">
         <v>13</v>
       </c>
       <c r="K149" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L149">
         <v>6</v>
@@ -7786,19 +8503,28 @@
       <c r="O149">
         <v>5</v>
       </c>
+      <c r="P149" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>47</v>
+      </c>
       <c r="R149" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="S149" t="s">
-        <v>61</v>
-      </c>
-      <c r="U149" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="W149" t="s">
-        <v>44</v>
-      </c>
-      <c r="X149">
+        <v>34</v>
+      </c>
+      <c r="X149" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB149">
         <v>9</v>
       </c>
     </row>
@@ -7810,7 +8536,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -7822,39 +8548,45 @@
         <v>-44</v>
       </c>
       <c r="G150" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H150" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I150" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J150">
         <v>7</v>
       </c>
       <c r="K150" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L150">
         <v>8</v>
       </c>
       <c r="M150" t="s">
-        <v>29</v>
-      </c>
-      <c r="R150" t="s">
-        <v>48</v>
+        <v>33</v>
+      </c>
+      <c r="P150" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>74</v>
       </c>
       <c r="S150" t="s">
-        <v>88</v>
-      </c>
-      <c r="U150" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W150" t="s">
-        <v>44</v>
-      </c>
-      <c r="X150">
+        <v>59</v>
+      </c>
+      <c r="X150" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z150" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB150">
         <v>9</v>
       </c>
     </row>
@@ -7866,7 +8598,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -7878,39 +8610,45 @@
         <v>49</v>
       </c>
       <c r="G151" t="s">
+        <v>41</v>
+      </c>
+      <c r="H151" t="s">
         <v>35</v>
       </c>
-      <c r="H151" t="s">
-        <v>31</v>
-      </c>
       <c r="I151" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J151">
         <v>6</v>
       </c>
       <c r="K151" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L151">
         <v>7</v>
       </c>
       <c r="M151" t="s">
-        <v>29</v>
-      </c>
-      <c r="R151" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="P151" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>40</v>
       </c>
       <c r="S151" t="s">
-        <v>41</v>
-      </c>
-      <c r="U151" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W151" t="s">
-        <v>44</v>
-      </c>
-      <c r="X151">
+        <v>34</v>
+      </c>
+      <c r="X151" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB151">
         <v>9</v>
       </c>
     </row>
@@ -7922,7 +8660,7 @@
         <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -7934,39 +8672,45 @@
         <v>43</v>
       </c>
       <c r="G152" t="s">
+        <v>41</v>
+      </c>
+      <c r="H152" t="s">
         <v>35</v>
       </c>
-      <c r="H152" t="s">
-        <v>31</v>
-      </c>
       <c r="I152" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J152">
         <v>4</v>
       </c>
       <c r="K152" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L152">
         <v>7</v>
       </c>
       <c r="M152" t="s">
-        <v>67</v>
-      </c>
-      <c r="R152" t="s">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="P152" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>47</v>
       </c>
       <c r="S152" t="s">
-        <v>75</v>
-      </c>
-      <c r="U152" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W152" t="s">
-        <v>44</v>
-      </c>
-      <c r="X152">
+        <v>34</v>
+      </c>
+      <c r="X152" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z152" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB152">
         <v>9</v>
       </c>
     </row>
@@ -7978,7 +8722,7 @@
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D153">
         <v>2</v>
@@ -7990,19 +8734,19 @@
         <v>39</v>
       </c>
       <c r="G153" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H153" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I153" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L153">
         <v>7</v>
@@ -8013,19 +8757,25 @@
       <c r="O153">
         <v>6</v>
       </c>
-      <c r="R153" t="s">
-        <v>35</v>
+      <c r="P153" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>47</v>
       </c>
       <c r="S153" t="s">
-        <v>36</v>
-      </c>
-      <c r="U153" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W153" t="s">
-        <v>44</v>
-      </c>
-      <c r="X153">
+        <v>41</v>
+      </c>
+      <c r="X153" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z153" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB153">
         <v>9</v>
       </c>
     </row>
@@ -8037,7 +8787,7 @@
         <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -8049,39 +8799,45 @@
         <v>39</v>
       </c>
       <c r="G154" t="s">
+        <v>41</v>
+      </c>
+      <c r="H154" t="s">
         <v>35</v>
       </c>
-      <c r="H154" t="s">
-        <v>31</v>
-      </c>
       <c r="I154" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J154">
         <v>12</v>
       </c>
       <c r="K154" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L154">
         <v>8</v>
       </c>
       <c r="M154" t="s">
-        <v>29</v>
-      </c>
-      <c r="R154" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="P154" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>47</v>
       </c>
       <c r="S154" t="s">
-        <v>83</v>
-      </c>
-      <c r="U154" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="W154" t="s">
-        <v>44</v>
-      </c>
-      <c r="X154">
+        <v>34</v>
+      </c>
+      <c r="X154" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z154" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB154">
         <v>9</v>
       </c>
     </row>
@@ -8093,7 +8849,7 @@
         <v>4</v>
       </c>
       <c r="C155" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -8105,36 +8861,45 @@
         <v>27</v>
       </c>
       <c r="G155" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H155" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I155" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J155">
         <v>-5</v>
       </c>
       <c r="K155" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L155">
         <v>6</v>
       </c>
-      <c r="R155" t="s">
-        <v>35</v>
+      <c r="P155" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>47</v>
       </c>
       <c r="S155" t="s">
-        <v>89</v>
-      </c>
-      <c r="U155" t="s">
-        <v>35</v>
+        <v>98</v>
+      </c>
+      <c r="T155" t="s">
+        <v>99</v>
       </c>
       <c r="W155" t="s">
-        <v>74</v>
-      </c>
-      <c r="X155">
+        <v>41</v>
+      </c>
+      <c r="X155" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z155" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB155">
         <v>9</v>
       </c>
     </row>
@@ -8146,7 +8911,7 @@
         <v>4</v>
       </c>
       <c r="C156" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D156">
         <v>2</v>
@@ -8158,39 +8923,45 @@
         <v>32</v>
       </c>
       <c r="G156" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H156" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I156" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J156">
         <v>-1</v>
       </c>
       <c r="K156" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L156">
         <v>9</v>
       </c>
       <c r="M156" t="s">
-        <v>29</v>
-      </c>
-      <c r="R156" t="s">
-        <v>48</v>
+        <v>33</v>
+      </c>
+      <c r="P156" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>40</v>
       </c>
       <c r="S156" t="s">
-        <v>88</v>
-      </c>
-      <c r="U156" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W156" t="s">
-        <v>44</v>
-      </c>
-      <c r="X156">
+        <v>59</v>
+      </c>
+      <c r="X156" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z156" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB156">
         <v>9</v>
       </c>
     </row>
@@ -8202,7 +8973,7 @@
         <v>4</v>
       </c>
       <c r="C157" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D157">
         <v>3</v>
@@ -8214,19 +8985,19 @@
         <v>33</v>
       </c>
       <c r="G157" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H157" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I157" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J157">
         <v>15</v>
       </c>
       <c r="K157" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L157">
         <v>6</v>
@@ -8237,19 +9008,28 @@
       <c r="O157">
         <v>6</v>
       </c>
+      <c r="P157" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>47</v>
+      </c>
       <c r="R157" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="S157" t="s">
-        <v>61</v>
-      </c>
-      <c r="U157" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="W157" t="s">
-        <v>44</v>
-      </c>
-      <c r="X157">
+        <v>34</v>
+      </c>
+      <c r="X157" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z157" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB157">
         <v>9</v>
       </c>
     </row>
@@ -8261,7 +9041,7 @@
         <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D158">
         <v>4</v>
@@ -8273,18 +9053,18 @@
         <v>18</v>
       </c>
       <c r="G158" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H158" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I158" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="J158">
         <v>0</v>
       </c>
-      <c r="X158">
+      <c r="AB158">
         <v>9</v>
       </c>
     </row>
@@ -8296,7 +9076,7 @@
         <v>4</v>
       </c>
       <c r="C159" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D159">
         <v>4</v>
@@ -8308,18 +9088,18 @@
         <v>18</v>
       </c>
       <c r="G159" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H159" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I159" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="J159">
         <v>0</v>
       </c>
-      <c r="X159">
+      <c r="AB159">
         <v>11</v>
       </c>
     </row>
@@ -8331,7 +9111,7 @@
         <v>4</v>
       </c>
       <c r="C160" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D160">
         <v>4</v>
@@ -8343,15 +9123,15 @@
         <v>18</v>
       </c>
       <c r="G160" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H160" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I160" t="s">
-        <v>59</v>
-      </c>
-      <c r="X160">
+        <v>72</v>
+      </c>
+      <c r="AB160">
         <v>10</v>
       </c>
     </row>
@@ -8363,7 +9143,7 @@
         <v>4</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -8375,13 +9155,13 @@
         <v>-40</v>
       </c>
       <c r="G161" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H161" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I161" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="162">
@@ -8392,7 +9172,7 @@
         <v>4</v>
       </c>
       <c r="C162" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -8404,19 +9184,19 @@
         <v>-35</v>
       </c>
       <c r="G162" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H162" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I162" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J162">
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N162">
         <v>18</v>
@@ -8424,19 +9204,22 @@
       <c r="O162">
         <v>5</v>
       </c>
-      <c r="Q162">
+      <c r="P162" t="s">
+        <v>66</v>
+      </c>
+      <c r="V162">
         <v>0</v>
       </c>
-      <c r="R162" t="s">
-        <v>35</v>
-      </c>
-      <c r="S162" t="s">
-        <v>61</v>
-      </c>
-      <c r="U162" t="s">
-        <v>30</v>
-      </c>
-      <c r="X162">
+      <c r="W162" t="s">
+        <v>41</v>
+      </c>
+      <c r="X162" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z162" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB162">
         <v>12</v>
       </c>
     </row>
